--- a/output/yearly_population_iteration_49_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_49_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7086</v>
+        <v>6921</v>
       </c>
       <c r="C2" t="n">
-        <v>5899</v>
+        <v>5584</v>
       </c>
       <c r="D2" t="n">
-        <v>27826</v>
+        <v>19900</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4491</v>
+        <v>4099</v>
       </c>
       <c r="C3" t="n">
-        <v>6602</v>
+        <v>5259</v>
       </c>
       <c r="D3" t="n">
-        <v>12489</v>
+        <v>12692</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3478</v>
+        <v>2937</v>
       </c>
       <c r="C4" t="n">
-        <v>6777</v>
+        <v>5883</v>
       </c>
       <c r="D4" t="n">
-        <v>6294</v>
+        <v>6670</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2182</v>
+        <v>1935</v>
       </c>
       <c r="C5" t="n">
-        <v>4975</v>
+        <v>4219</v>
       </c>
       <c r="D5" t="n">
-        <v>2413</v>
+        <v>2541</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1207</v>
+        <v>1093</v>
       </c>
       <c r="C6" t="n">
-        <v>3197</v>
+        <v>2214</v>
       </c>
       <c r="D6" t="n">
-        <v>1049</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>567</v>
+        <v>497</v>
       </c>
       <c r="C7" t="n">
-        <v>1856</v>
+        <v>1283</v>
       </c>
       <c r="D7" t="n">
-        <v>635</v>
+        <v>649</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>206</v>
+        <v>190</v>
       </c>
       <c r="C8" t="n">
-        <v>889</v>
+        <v>618</v>
       </c>
       <c r="D8" t="n">
-        <v>429</v>
+        <v>439</v>
       </c>
     </row>
     <row r="9">
@@ -878,10 +878,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="C9" t="n">
-        <v>403</v>
+        <v>321</v>
       </c>
       <c r="D9" t="n">
         <v>306</v>
@@ -895,10 +895,10 @@
         <v>39</v>
       </c>
       <c r="C10" t="n">
-        <v>222</v>
+        <v>214</v>
       </c>
       <c r="D10" t="n">
-        <v>245</v>
+        <v>251</v>
       </c>
     </row>
     <row r="11">
@@ -909,7 +909,7 @@
         <v>27</v>
       </c>
       <c r="C11" t="n">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="D11" t="n">
         <v>203</v>
@@ -923,7 +923,7 @@
         <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D12" t="n">
         <v>161</v>
@@ -937,10 +937,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D13" t="n">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
         <v>77</v>
       </c>
       <c r="D14" t="n">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16">
@@ -979,10 +979,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="17">
@@ -993,10 +993,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18">
@@ -1007,10 +1007,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -1024,7 +1024,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20">
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1049,7 +1049,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="D21" t="n">
         <v>9</v>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7535</v>
+        <v>8994</v>
       </c>
       <c r="C2" t="n">
-        <v>6106</v>
+        <v>7729</v>
       </c>
       <c r="D2" t="n">
-        <v>26664</v>
+        <v>22603</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4581</v>
+        <v>4371</v>
       </c>
       <c r="C3" t="n">
-        <v>5544</v>
+        <v>4746</v>
       </c>
       <c r="D3" t="n">
-        <v>13735</v>
+        <v>12856</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3376</v>
+        <v>2953</v>
       </c>
       <c r="C4" t="n">
-        <v>6553</v>
+        <v>5449</v>
       </c>
       <c r="D4" t="n">
-        <v>7113</v>
+        <v>7507</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2405</v>
+        <v>2123</v>
       </c>
       <c r="C5" t="n">
-        <v>5636</v>
+        <v>4889</v>
       </c>
       <c r="D5" t="n">
-        <v>2912</v>
+        <v>3113</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1468</v>
+        <v>1331</v>
       </c>
       <c r="C6" t="n">
-        <v>3920</v>
+        <v>3134</v>
       </c>
       <c r="D6" t="n">
-        <v>1244</v>
+        <v>1321</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>747</v>
+        <v>678</v>
       </c>
       <c r="C7" t="n">
-        <v>2446</v>
+        <v>1698</v>
       </c>
       <c r="D7" t="n">
-        <v>683</v>
+        <v>713</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>314</v>
+        <v>286</v>
       </c>
       <c r="C8" t="n">
-        <v>1287</v>
+        <v>917</v>
       </c>
       <c r="D8" t="n">
-        <v>454</v>
+        <v>461</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="C9" t="n">
-        <v>602</v>
+        <v>445</v>
       </c>
       <c r="D9" t="n">
-        <v>316</v>
+        <v>322</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C10" t="n">
-        <v>290</v>
+        <v>259</v>
       </c>
       <c r="D10" t="n">
-        <v>250</v>
+        <v>253</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C11" t="n">
         <v>186</v>
       </c>
       <c r="D11" t="n">
-        <v>204</v>
+        <v>207</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="D12" t="n">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="13">
@@ -1248,10 +1248,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="D13" t="n">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="14">
@@ -1262,10 +1262,10 @@
         <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D14" t="n">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="17">
@@ -1304,10 +1304,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -1318,10 +1318,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -1335,7 +1335,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20">
@@ -1346,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1360,7 +1360,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="D21" t="n">
         <v>10</v>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8172</v>
+        <v>9492</v>
       </c>
       <c r="C2" t="n">
-        <v>7017</v>
+        <v>11148</v>
       </c>
       <c r="D2" t="n">
-        <v>22143</v>
+        <v>29042</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4689</v>
+        <v>5149</v>
       </c>
       <c r="C3" t="n">
-        <v>5178</v>
+        <v>5320</v>
       </c>
       <c r="D3" t="n">
-        <v>14407</v>
+        <v>13260</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3284</v>
+        <v>3012</v>
       </c>
       <c r="C4" t="n">
-        <v>5927</v>
+        <v>4966</v>
       </c>
       <c r="D4" t="n">
-        <v>7782</v>
+        <v>8028</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2479</v>
+        <v>2191</v>
       </c>
       <c r="C5" t="n">
-        <v>5843</v>
+        <v>4987</v>
       </c>
       <c r="D5" t="n">
-        <v>3428</v>
+        <v>3693</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1673</v>
+        <v>1512</v>
       </c>
       <c r="C6" t="n">
-        <v>4577</v>
+        <v>3862</v>
       </c>
       <c r="D6" t="n">
-        <v>1439</v>
+        <v>1548</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>930</v>
+        <v>849</v>
       </c>
       <c r="C7" t="n">
-        <v>2998</v>
+        <v>2285</v>
       </c>
       <c r="D7" t="n">
-        <v>753</v>
+        <v>795</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>421</v>
+        <v>396</v>
       </c>
       <c r="C8" t="n">
-        <v>1716</v>
+        <v>1238</v>
       </c>
       <c r="D8" t="n">
-        <v>474</v>
+        <v>486</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="C9" t="n">
-        <v>856</v>
+        <v>625</v>
       </c>
       <c r="D9" t="n">
-        <v>330</v>
+        <v>337</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C10" t="n">
-        <v>397</v>
+        <v>329</v>
       </c>
       <c r="D10" t="n">
-        <v>252</v>
+        <v>256</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C11" t="n">
-        <v>219</v>
+        <v>210</v>
       </c>
       <c r="D11" t="n">
-        <v>207</v>
+        <v>210</v>
       </c>
     </row>
     <row r="12">
@@ -1545,10 +1545,10 @@
         <v>19</v>
       </c>
       <c r="C12" t="n">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D12" t="n">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="D13" t="n">
-        <v>127</v>
+        <v>130</v>
       </c>
     </row>
     <row r="14">
@@ -1573,10 +1573,10 @@
         <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D14" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="15">
@@ -1587,10 +1587,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
     </row>
     <row r="16">
@@ -1601,10 +1601,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="17">
@@ -1615,7 +1615,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="D17" t="n">
         <v>52</v>
@@ -1629,10 +1629,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -1646,7 +1646,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20">
@@ -1657,7 +1657,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1671,7 +1671,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="D21" t="n">
         <v>11</v>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7587</v>
+        <v>8657</v>
       </c>
       <c r="C2" t="n">
-        <v>4827</v>
+        <v>7402</v>
       </c>
       <c r="D2" t="n">
-        <v>18405</v>
+        <v>23510</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5754</v>
+        <v>5900</v>
       </c>
       <c r="C3" t="n">
-        <v>8203</v>
+        <v>8577</v>
       </c>
       <c r="D3" t="n">
-        <v>15529</v>
+        <v>14841</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2290</v>
+        <v>2024</v>
       </c>
       <c r="C4" t="n">
-        <v>8852</v>
+        <v>7600</v>
       </c>
       <c r="D4" t="n">
-        <v>7449</v>
+        <v>7834</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1545</v>
+        <v>1397</v>
       </c>
       <c r="C5" t="n">
-        <v>4485</v>
+        <v>3784</v>
       </c>
       <c r="D5" t="n">
-        <v>2331</v>
+        <v>2545</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>859</v>
+        <v>784</v>
       </c>
       <c r="C6" t="n">
-        <v>2938</v>
+        <v>2239</v>
       </c>
       <c r="D6" t="n">
-        <v>737</v>
+        <v>779</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>389</v>
+        <v>365</v>
       </c>
       <c r="C7" t="n">
-        <v>1681</v>
+        <v>1213</v>
       </c>
       <c r="D7" t="n">
-        <v>464</v>
+        <v>476</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="C8" t="n">
-        <v>838</v>
+        <v>612</v>
       </c>
       <c r="D8" t="n">
-        <v>323</v>
+        <v>330</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C9" t="n">
-        <v>389</v>
+        <v>322</v>
       </c>
       <c r="D9" t="n">
-        <v>246</v>
+        <v>250</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C10" t="n">
-        <v>214</v>
+        <v>205</v>
       </c>
       <c r="D10" t="n">
-        <v>202</v>
+        <v>205</v>
       </c>
     </row>
     <row r="11">
@@ -1842,10 +1842,10 @@
         <v>17</v>
       </c>
       <c r="C11" t="n">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D11" t="n">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="D12" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
     </row>
     <row r="13">
@@ -1870,10 +1870,10 @@
         <v>6</v>
       </c>
       <c r="C13" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="14">
@@ -1884,10 +1884,10 @@
         <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="D15" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="16">
@@ -1912,7 +1912,7 @@
         <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="D16" t="n">
         <v>50</v>
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D17" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="18">
@@ -1943,7 +1943,7 @@
         <v>30</v>
       </c>
       <c r="D18" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="19">
@@ -1954,7 +1954,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D19" t="n">
         <v>15</v>
@@ -1968,7 +1968,7 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="D20" t="n">
         <v>11</v>
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4697</v>
+        <v>5049</v>
       </c>
       <c r="C2" t="n">
-        <v>2741</v>
+        <v>3264</v>
       </c>
       <c r="D2" t="n">
-        <v>12973</v>
+        <v>16471</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5663</v>
+        <v>6125</v>
       </c>
       <c r="C3" t="n">
-        <v>6064</v>
+        <v>7255</v>
       </c>
       <c r="D3" t="n">
-        <v>15174</v>
+        <v>15353</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3130</v>
+        <v>3085</v>
       </c>
       <c r="C4" t="n">
-        <v>8623</v>
+        <v>8202</v>
       </c>
       <c r="D4" t="n">
-        <v>8457</v>
+        <v>8747</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1729</v>
+        <v>1545</v>
       </c>
       <c r="C5" t="n">
-        <v>6409</v>
+        <v>5462</v>
       </c>
       <c r="D5" t="n">
-        <v>2943</v>
+        <v>3251</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1018</v>
+        <v>951</v>
       </c>
       <c r="C6" t="n">
-        <v>3651</v>
+        <v>2938</v>
       </c>
       <c r="D6" t="n">
-        <v>902</v>
+        <v>961</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>366</v>
+        <v>345</v>
       </c>
       <c r="C7" t="n">
-        <v>2144</v>
+        <v>1611</v>
       </c>
       <c r="D7" t="n">
-        <v>506</v>
+        <v>517</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C8" t="n">
-        <v>1107</v>
+        <v>802</v>
       </c>
       <c r="D8" t="n">
-        <v>337</v>
+        <v>345</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C9" t="n">
-        <v>434</v>
+        <v>380</v>
       </c>
       <c r="D9" t="n">
-        <v>255</v>
+        <v>262</v>
       </c>
     </row>
     <row r="10">
@@ -2139,7 +2139,7 @@
         <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="D10" t="n">
         <v>211</v>
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="D11" t="n">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="12">
@@ -2167,10 +2167,10 @@
         <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="D12" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="13">
@@ -2181,10 +2181,10 @@
         <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D13" t="n">
-        <v>97</v>
+        <v>101</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D14" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="15">
@@ -2209,7 +2209,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="D15" t="n">
         <v>49</v>
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D16" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="17">
@@ -2240,7 +2240,7 @@
         <v>29</v>
       </c>
       <c r="D17" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="18">
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D18" t="n">
         <v>14</v>
@@ -2265,7 +2265,7 @@
         <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="D19" t="n">
         <v>10</v>
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6207</v>
+        <v>4876</v>
       </c>
       <c r="C2" t="n">
-        <v>10662</v>
+        <v>5235</v>
       </c>
       <c r="D2" t="n">
-        <v>19928</v>
+        <v>25772</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4462</v>
+        <v>4751</v>
       </c>
       <c r="C3" t="n">
-        <v>3992</v>
+        <v>4657</v>
       </c>
       <c r="D3" t="n">
-        <v>13854</v>
+        <v>14457</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3604</v>
+        <v>3821</v>
       </c>
       <c r="C4" t="n">
-        <v>7190</v>
+        <v>7549</v>
       </c>
       <c r="D4" t="n">
-        <v>9296</v>
+        <v>9622</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2062</v>
+        <v>1950</v>
       </c>
       <c r="C5" t="n">
-        <v>7378</v>
+        <v>6742</v>
       </c>
       <c r="D5" t="n">
-        <v>3700</v>
+        <v>4049</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1214</v>
+        <v>1108</v>
       </c>
       <c r="C6" t="n">
-        <v>4833</v>
+        <v>4071</v>
       </c>
       <c r="D6" t="n">
-        <v>1183</v>
+        <v>1299</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>541</v>
+        <v>521</v>
       </c>
       <c r="C7" t="n">
-        <v>2813</v>
+        <v>2224</v>
       </c>
       <c r="D7" t="n">
-        <v>555</v>
+        <v>576</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="C8" t="n">
-        <v>1534</v>
+        <v>1150</v>
       </c>
       <c r="D8" t="n">
-        <v>355</v>
+        <v>368</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C9" t="n">
-        <v>688</v>
+        <v>552</v>
       </c>
       <c r="D9" t="n">
-        <v>262</v>
+        <v>269</v>
       </c>
     </row>
     <row r="10">
@@ -2450,10 +2450,10 @@
         <v>20</v>
       </c>
       <c r="C10" t="n">
-        <v>305</v>
+        <v>283</v>
       </c>
       <c r="D10" t="n">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="D11" t="n">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="12">
@@ -2478,10 +2478,10 @@
         <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="D12" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D13" t="n">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D14" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
     </row>
     <row r="15">
@@ -2520,7 +2520,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D15" t="n">
         <v>48</v>
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D16" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17">
@@ -2551,7 +2551,7 @@
         <v>31</v>
       </c>
       <c r="D17" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="18">
@@ -2562,7 +2562,7 @@
         <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D18" t="n">
         <v>13</v>
@@ -2576,7 +2576,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D19" t="n">
         <v>7</v>
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3677</v>
+        <v>2888</v>
       </c>
       <c r="C2" t="n">
-        <v>4967</v>
+        <v>2371</v>
       </c>
       <c r="D2" t="n">
-        <v>13907</v>
+        <v>17767</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4747</v>
+        <v>4610</v>
       </c>
       <c r="C3" t="n">
-        <v>6111</v>
+        <v>4703</v>
       </c>
       <c r="D3" t="n">
-        <v>14175</v>
+        <v>15377</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3945</v>
+        <v>4205</v>
       </c>
       <c r="C4" t="n">
-        <v>6686</v>
+        <v>7189</v>
       </c>
       <c r="D4" t="n">
-        <v>9888</v>
+        <v>10255</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2152</v>
+        <v>2022</v>
       </c>
       <c r="C5" t="n">
-        <v>8531</v>
+        <v>7845</v>
       </c>
       <c r="D5" t="n">
-        <v>3911</v>
+        <v>4383</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>993</v>
+        <v>942</v>
       </c>
       <c r="C6" t="n">
-        <v>5716</v>
+        <v>4958</v>
       </c>
       <c r="D6" t="n">
-        <v>1167</v>
+        <v>1281</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="C7" t="n">
-        <v>2884</v>
+        <v>2258</v>
       </c>
       <c r="D7" t="n">
-        <v>561</v>
+        <v>584</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C8" t="n">
-        <v>1140</v>
+        <v>912</v>
       </c>
       <c r="D8" t="n">
-        <v>374</v>
+        <v>387</v>
       </c>
     </row>
     <row r="9">
@@ -2747,10 +2747,10 @@
         <v>18</v>
       </c>
       <c r="C9" t="n">
-        <v>298</v>
+        <v>277</v>
       </c>
       <c r="D9" t="n">
-        <v>287</v>
+        <v>293</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>183</v>
+        <v>190</v>
       </c>
       <c r="D10" t="n">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="11">
@@ -2775,10 +2775,10 @@
         <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="D11" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D12" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="13">
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
     </row>
     <row r="14">
@@ -2817,7 +2817,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="D14" t="n">
         <v>47</v>
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D15" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="16">
@@ -2848,7 +2848,7 @@
         <v>30</v>
       </c>
       <c r="D16" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="17">
@@ -2859,7 +2859,7 @@
         <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D17" t="n">
         <v>12</v>
@@ -2873,7 +2873,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D18" t="n">
         <v>6</v>
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4628</v>
+        <v>3920</v>
       </c>
       <c r="C2" t="n">
-        <v>4735</v>
+        <v>3090</v>
       </c>
       <c r="D2" t="n">
-        <v>12002</v>
+        <v>13201</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3673</v>
+        <v>3327</v>
       </c>
       <c r="C3" t="n">
-        <v>4978</v>
+        <v>3179</v>
       </c>
       <c r="D3" t="n">
-        <v>13322</v>
+        <v>14668</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3728</v>
+        <v>3828</v>
       </c>
       <c r="C4" t="n">
-        <v>6276</v>
+        <v>5891</v>
       </c>
       <c r="D4" t="n">
-        <v>10245</v>
+        <v>10779</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2562</v>
+        <v>2577</v>
       </c>
       <c r="C5" t="n">
-        <v>7602</v>
+        <v>7454</v>
       </c>
       <c r="D5" t="n">
-        <v>4652</v>
+        <v>5151</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1306</v>
+        <v>1243</v>
       </c>
       <c r="C6" t="n">
-        <v>6964</v>
+        <v>6207</v>
       </c>
       <c r="D6" t="n">
-        <v>1520</v>
+        <v>1723</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>371</v>
+        <v>361</v>
       </c>
       <c r="C7" t="n">
-        <v>4021</v>
+        <v>3412</v>
       </c>
       <c r="D7" t="n">
-        <v>637</v>
+        <v>666</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C8" t="n">
-        <v>1794</v>
+        <v>1430</v>
       </c>
       <c r="D8" t="n">
-        <v>394</v>
+        <v>410</v>
       </c>
     </row>
     <row r="9">
@@ -3058,10 +3058,10 @@
         <v>23</v>
       </c>
       <c r="C9" t="n">
-        <v>578</v>
+        <v>496</v>
       </c>
       <c r="D9" t="n">
-        <v>294</v>
+        <v>302</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C10" t="n">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D10" t="n">
-        <v>174</v>
+        <v>177</v>
       </c>
     </row>
     <row r="11">
@@ -3086,10 +3086,10 @@
         <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="D11" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D12" t="n">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
     </row>
     <row r="14">
@@ -3128,7 +3128,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D14" t="n">
         <v>47</v>
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D15" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16">
@@ -3156,7 +3156,7 @@
         <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D16" t="n">
         <v>20</v>
@@ -3170,7 +3170,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="D17" t="n">
         <v>10</v>
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D18" t="n">
         <v>2</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3210</v>
+        <v>3059</v>
       </c>
       <c r="C2" t="n">
-        <v>3037</v>
+        <v>2467</v>
       </c>
       <c r="D2" t="n">
-        <v>9540</v>
+        <v>9375</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3486</v>
+        <v>3084</v>
       </c>
       <c r="C3" t="n">
-        <v>4476</v>
+        <v>2876</v>
       </c>
       <c r="D3" t="n">
-        <v>12438</v>
+        <v>13694</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3416</v>
+        <v>3357</v>
       </c>
       <c r="C4" t="n">
-        <v>5802</v>
+        <v>4762</v>
       </c>
       <c r="D4" t="n">
-        <v>10543</v>
+        <v>11077</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2758</v>
+        <v>2830</v>
       </c>
       <c r="C5" t="n">
-        <v>7191</v>
+        <v>7000</v>
       </c>
       <c r="D5" t="n">
-        <v>5145</v>
+        <v>5741</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1541</v>
+        <v>1493</v>
       </c>
       <c r="C6" t="n">
-        <v>7453</v>
+        <v>6862</v>
       </c>
       <c r="D6" t="n">
-        <v>1817</v>
+        <v>2032</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>334</v>
+        <v>340</v>
       </c>
       <c r="C7" t="n">
-        <v>5016</v>
+        <v>4356</v>
       </c>
       <c r="D7" t="n">
-        <v>704</v>
+        <v>748</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C8" t="n">
-        <v>2329</v>
+        <v>1905</v>
       </c>
       <c r="D8" t="n">
-        <v>406</v>
+        <v>433</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C9" t="n">
-        <v>673</v>
+        <v>596</v>
       </c>
       <c r="D9" t="n">
-        <v>292</v>
+        <v>300</v>
       </c>
     </row>
     <row r="10">
@@ -3383,10 +3383,10 @@
         <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="D10" t="n">
-        <v>177</v>
+        <v>180</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="D11" t="n">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="D12" t="n">
-        <v>92</v>
+        <v>95</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D13" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D14" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="15">
@@ -3453,7 +3453,7 @@
         <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D15" t="n">
         <v>19</v>
@@ -3467,7 +3467,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="D16" t="n">
         <v>9</v>
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
         <v>1</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4607</v>
+        <v>5492</v>
       </c>
       <c r="C2" t="n">
-        <v>14155</v>
+        <v>10190</v>
       </c>
       <c r="D2" t="n">
-        <v>17150</v>
+        <v>12431</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2851</v>
+        <v>2585</v>
       </c>
       <c r="C3" t="n">
-        <v>3475</v>
+        <v>2426</v>
       </c>
       <c r="D3" t="n">
-        <v>11294</v>
+        <v>12374</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3019</v>
+        <v>2831</v>
       </c>
       <c r="C4" t="n">
-        <v>5121</v>
+        <v>3802</v>
       </c>
       <c r="D4" t="n">
-        <v>10495</v>
+        <v>11010</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2718</v>
+        <v>2779</v>
       </c>
       <c r="C5" t="n">
-        <v>6481</v>
+        <v>5976</v>
       </c>
       <c r="D5" t="n">
-        <v>5714</v>
+        <v>6334</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1815</v>
+        <v>1816</v>
       </c>
       <c r="C6" t="n">
-        <v>7289</v>
+        <v>6857</v>
       </c>
       <c r="D6" t="n">
-        <v>2209</v>
+        <v>2504</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="C7" t="n">
-        <v>5921</v>
+        <v>5312</v>
       </c>
       <c r="D7" t="n">
-        <v>827</v>
+        <v>903</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="C8" t="n">
-        <v>3298</v>
+        <v>2811</v>
       </c>
       <c r="D8" t="n">
-        <v>433</v>
+        <v>465</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C9" t="n">
-        <v>1214</v>
+        <v>1031</v>
       </c>
       <c r="D9" t="n">
-        <v>300</v>
+        <v>311</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C10" t="n">
-        <v>359</v>
+        <v>349</v>
       </c>
       <c r="D10" t="n">
-        <v>185</v>
+        <v>191</v>
       </c>
     </row>
     <row r="11">
@@ -3708,7 +3708,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="D11" t="n">
         <v>138</v>
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="D12" t="n">
-        <v>94</v>
+        <v>97</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="D13" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
+        <v>39</v>
+      </c>
+      <c r="D14" t="n">
         <v>38</v>
-      </c>
-      <c r="D14" t="n">
-        <v>36</v>
       </c>
     </row>
     <row r="15">
@@ -3764,7 +3764,7 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D15" t="n">
         <v>18</v>
@@ -3778,7 +3778,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="D16" t="n">
         <v>8</v>
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7331</v>
+        <v>5682</v>
       </c>
       <c r="C2" t="n">
-        <v>9003</v>
+        <v>4811</v>
       </c>
       <c r="D2" t="n">
-        <v>3070</v>
+        <v>6231</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3334</v>
+        <v>3885</v>
       </c>
       <c r="C2" t="n">
-        <v>8153</v>
+        <v>5706</v>
       </c>
       <c r="D2" t="n">
-        <v>12759</v>
+        <v>9149</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3775</v>
+        <v>3622</v>
       </c>
       <c r="C3" t="n">
-        <v>6173</v>
+        <v>4495</v>
       </c>
       <c r="D3" t="n">
-        <v>12507</v>
+        <v>13414</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4055</v>
+        <v>3984</v>
       </c>
       <c r="C4" t="n">
-        <v>7302</v>
+        <v>5707</v>
       </c>
       <c r="D4" t="n">
-        <v>10741</v>
+        <v>11289</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1727</v>
+        <v>1780</v>
       </c>
       <c r="C5" t="n">
-        <v>9954</v>
+        <v>9267</v>
       </c>
       <c r="D5" t="n">
-        <v>5196</v>
+        <v>5848</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="C6" t="n">
-        <v>7159</v>
+        <v>6616</v>
       </c>
       <c r="D6" t="n">
-        <v>1787</v>
+        <v>1996</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="C7" t="n">
-        <v>3232</v>
+        <v>2754</v>
       </c>
       <c r="D7" t="n">
-        <v>529</v>
+        <v>570</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C8" t="n">
-        <v>1189</v>
+        <v>1010</v>
       </c>
       <c r="D8" t="n">
-        <v>294</v>
+        <v>304</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C9" t="n">
-        <v>351</v>
+        <v>342</v>
       </c>
       <c r="D9" t="n">
-        <v>181</v>
+        <v>187</v>
       </c>
     </row>
     <row r="10">
@@ -4316,7 +4316,7 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="D10" t="n">
         <v>135</v>
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="D11" t="n">
-        <v>92</v>
+        <v>95</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="D12" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
+        <v>38</v>
+      </c>
+      <c r="D13" t="n">
         <v>37</v>
-      </c>
-      <c r="D13" t="n">
-        <v>35</v>
       </c>
     </row>
     <row r="14">
@@ -4372,7 +4372,7 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D14" t="n">
         <v>17</v>
@@ -4386,7 +4386,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="D15" t="n">
         <v>7</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7403</v>
+        <v>6269</v>
       </c>
       <c r="C2" t="n">
-        <v>4617</v>
+        <v>3299</v>
       </c>
       <c r="D2" t="n">
-        <v>13288</v>
+        <v>15458</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3113</v>
+        <v>2414</v>
       </c>
       <c r="C3" t="n">
-        <v>4537</v>
+        <v>2463</v>
       </c>
       <c r="D3" t="n">
-        <v>1155</v>
+        <v>1735</v>
       </c>
     </row>
     <row r="4">
@@ -4655,7 +4655,7 @@
         <v>26</v>
       </c>
       <c r="C12" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D12" t="n">
         <v>199</v>
@@ -4669,7 +4669,7 @@
         <v>19</v>
       </c>
       <c r="C13" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D13" t="n">
         <v>170</v>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5400</v>
+        <v>4628</v>
       </c>
       <c r="C2" t="n">
-        <v>4503</v>
+        <v>3301</v>
       </c>
       <c r="D2" t="n">
-        <v>21709</v>
+        <v>13245</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4320</v>
+        <v>3565</v>
       </c>
       <c r="C3" t="n">
-        <v>3951</v>
+        <v>2534</v>
       </c>
       <c r="D3" t="n">
-        <v>3108</v>
+        <v>3912</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1386</v>
+        <v>1082</v>
       </c>
       <c r="C4" t="n">
-        <v>2700</v>
+        <v>1509</v>
       </c>
       <c r="D4" t="n">
-        <v>1414</v>
+        <v>1530</v>
       </c>
     </row>
     <row r="5">
@@ -4879,7 +4879,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C6" t="n">
         <v>411</v>
@@ -4893,7 +4893,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C7" t="n">
         <v>409</v>
@@ -4924,7 +4924,7 @@
         <v>84</v>
       </c>
       <c r="C9" t="n">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="D9" t="n">
         <v>363</v>
@@ -4938,7 +4938,7 @@
         <v>63</v>
       </c>
       <c r="C10" t="n">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="D10" t="n">
         <v>352</v>
@@ -4949,7 +4949,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C11" t="n">
         <v>166</v>
@@ -4966,7 +4966,7 @@
         <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D12" t="n">
         <v>206</v>
@@ -4983,7 +4983,7 @@
         <v>103</v>
       </c>
       <c r="D13" t="n">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="14">
@@ -4994,10 +4994,10 @@
         <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="15">
@@ -5022,7 +5022,7 @@
         <v>13</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D16" t="n">
         <v>98</v>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6159</v>
+        <v>6001</v>
       </c>
       <c r="C2" t="n">
-        <v>10452</v>
+        <v>7350</v>
       </c>
       <c r="D2" t="n">
-        <v>22361</v>
+        <v>26381</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3993</v>
+        <v>3369</v>
       </c>
       <c r="C3" t="n">
-        <v>3680</v>
+        <v>2557</v>
       </c>
       <c r="D3" t="n">
-        <v>5860</v>
+        <v>5123</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2429</v>
+        <v>1998</v>
       </c>
       <c r="C4" t="n">
-        <v>3352</v>
+        <v>2068</v>
       </c>
       <c r="D4" t="n">
-        <v>1696</v>
+        <v>1926</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>617</v>
+        <v>503</v>
       </c>
       <c r="C5" t="n">
-        <v>1572</v>
+        <v>933</v>
       </c>
       <c r="D5" t="n">
-        <v>1180</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="6">
@@ -5190,10 +5190,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C6" t="n">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="D6" t="n">
         <v>910</v>
@@ -5204,7 +5204,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C7" t="n">
         <v>409</v>
@@ -5221,7 +5221,7 @@
         <v>125</v>
       </c>
       <c r="C8" t="n">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="D8" t="n">
         <v>462</v>
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C9" t="n">
         <v>268</v>
       </c>
       <c r="D9" t="n">
-        <v>372</v>
+        <v>368</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C10" t="n">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>350</v>
       </c>
     </row>
     <row r="11">
@@ -5263,7 +5263,7 @@
         <v>47</v>
       </c>
       <c r="C11" t="n">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D11" t="n">
         <v>280</v>
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C12" t="n">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D12" t="n">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="13">
@@ -5305,10 +5305,10 @@
         <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="15">
@@ -5322,7 +5322,7 @@
         <v>77</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="16">
@@ -5333,7 +5333,7 @@
         <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D16" t="n">
         <v>99</v>
@@ -5350,7 +5350,7 @@
         <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18">
@@ -5361,10 +5361,10 @@
         <v>10</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="19">
@@ -5375,7 +5375,7 @@
         <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D19" t="n">
         <v>41</v>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7249</v>
+        <v>6247</v>
       </c>
       <c r="C2" t="n">
-        <v>7277</v>
+        <v>4111</v>
       </c>
       <c r="D2" t="n">
-        <v>25200</v>
+        <v>27572</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4118</v>
+        <v>3777</v>
       </c>
       <c r="C3" t="n">
-        <v>6236</v>
+        <v>4407</v>
       </c>
       <c r="D3" t="n">
-        <v>7955</v>
+        <v>7993</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2737</v>
+        <v>2268</v>
       </c>
       <c r="C4" t="n">
-        <v>3458</v>
+        <v>2292</v>
       </c>
       <c r="D4" t="n">
-        <v>2403</v>
+        <v>2432</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1250</v>
+        <v>1043</v>
       </c>
       <c r="C5" t="n">
-        <v>2446</v>
+        <v>1512</v>
       </c>
       <c r="D5" t="n">
-        <v>1221</v>
+        <v>1307</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>330</v>
+        <v>281</v>
       </c>
       <c r="C6" t="n">
-        <v>944</v>
+        <v>617</v>
       </c>
       <c r="D6" t="n">
-        <v>944</v>
+        <v>941</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C7" t="n">
         <v>354</v>
       </c>
       <c r="D7" t="n">
-        <v>659</v>
+        <v>668</v>
       </c>
     </row>
     <row r="8">
@@ -5529,10 +5529,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C8" t="n">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="D8" t="n">
         <v>484</v>
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C9" t="n">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="D9" t="n">
-        <v>378</v>
+        <v>375</v>
       </c>
     </row>
     <row r="10">
@@ -5560,10 +5560,10 @@
         <v>71</v>
       </c>
       <c r="C10" t="n">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>349</v>
       </c>
     </row>
     <row r="11">
@@ -5574,10 +5574,10 @@
         <v>50</v>
       </c>
       <c r="C11" t="n">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="D11" t="n">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C12" t="n">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="D12" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="13">
@@ -5616,10 +5616,10 @@
         <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="15">
@@ -5630,10 +5630,10 @@
         <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D15" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="16">
@@ -5647,7 +5647,7 @@
         <v>73</v>
       </c>
       <c r="D16" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17">
@@ -5658,7 +5658,7 @@
         <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D17" t="n">
         <v>79</v>
@@ -5672,10 +5672,10 @@
         <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D18" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="19">
@@ -5689,7 +5689,7 @@
         <v>62</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="20">
@@ -5700,7 +5700,7 @@
         <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D20" t="n">
         <v>24</v>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7995</v>
+        <v>6500</v>
       </c>
       <c r="C2" t="n">
-        <v>10482</v>
+        <v>12561</v>
       </c>
       <c r="D2" t="n">
-        <v>23989</v>
+        <v>25422</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4091</v>
+        <v>3637</v>
       </c>
       <c r="C3" t="n">
-        <v>5544</v>
+        <v>3481</v>
       </c>
       <c r="D3" t="n">
-        <v>9423</v>
+        <v>9789</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2113</v>
+        <v>1875</v>
       </c>
       <c r="C4" t="n">
-        <v>4087</v>
+        <v>2853</v>
       </c>
       <c r="D4" t="n">
-        <v>2917</v>
+        <v>2923</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1047</v>
+        <v>877</v>
       </c>
       <c r="C5" t="n">
-        <v>2150</v>
+        <v>1395</v>
       </c>
       <c r="D5" t="n">
-        <v>1114</v>
+        <v>1193</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>370</v>
+        <v>315</v>
       </c>
       <c r="C6" t="n">
-        <v>1146</v>
+        <v>726</v>
       </c>
       <c r="D6" t="n">
-        <v>754</v>
+        <v>756</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="C7" t="n">
-        <v>410</v>
+        <v>308</v>
       </c>
       <c r="D7" t="n">
-        <v>512</v>
+        <v>524</v>
       </c>
     </row>
     <row r="8">
@@ -5843,10 +5843,10 @@
         <v>58</v>
       </c>
       <c r="C8" t="n">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="D8" t="n">
-        <v>364</v>
+        <v>361</v>
       </c>
     </row>
     <row r="9">
@@ -5860,7 +5860,7 @@
         <v>199</v>
       </c>
       <c r="D9" t="n">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="10">
@@ -5874,7 +5874,7 @@
         <v>150</v>
       </c>
       <c r="D10" t="n">
-        <v>237</v>
+        <v>239</v>
       </c>
     </row>
     <row r="11">
@@ -5885,10 +5885,10 @@
         <v>21</v>
       </c>
       <c r="C11" t="n">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D11" t="n">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="12">
@@ -5902,7 +5902,7 @@
         <v>91</v>
       </c>
       <c r="D12" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="13">
@@ -5916,7 +5916,7 @@
         <v>74</v>
       </c>
       <c r="D13" t="n">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="14">
@@ -5927,10 +5927,10 @@
         <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D14" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="15">
@@ -5941,7 +5941,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D15" t="n">
         <v>79</v>
@@ -5958,7 +5958,7 @@
         <v>38</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -5969,7 +5969,7 @@
         <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D17" t="n">
         <v>50</v>
@@ -5980,7 +5980,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C18" t="n">
         <v>33</v>
@@ -6000,7 +6000,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -6011,7 +6011,7 @@
         <v>2</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>15</v>
@@ -6025,7 +6025,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D21" t="n">
         <v>6</v>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6808</v>
+        <v>5352</v>
       </c>
       <c r="C2" t="n">
-        <v>10282</v>
+        <v>6820</v>
       </c>
       <c r="D2" t="n">
-        <v>21937</v>
+        <v>18751</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5028</v>
+        <v>4233</v>
       </c>
       <c r="C3" t="n">
-        <v>7252</v>
+        <v>7701</v>
       </c>
       <c r="D3" t="n">
-        <v>11176</v>
+        <v>11804</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2729</v>
+        <v>2440</v>
       </c>
       <c r="C4" t="n">
-        <v>4883</v>
+        <v>3185</v>
       </c>
       <c r="D4" t="n">
-        <v>4111</v>
+        <v>4284</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1411</v>
+        <v>1227</v>
       </c>
       <c r="C5" t="n">
-        <v>3239</v>
+        <v>2247</v>
       </c>
       <c r="D5" t="n">
-        <v>1443</v>
+        <v>1494</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>651</v>
+        <v>561</v>
       </c>
       <c r="C6" t="n">
-        <v>1689</v>
+        <v>1108</v>
       </c>
       <c r="D6" t="n">
-        <v>812</v>
+        <v>833</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>214</v>
+        <v>188</v>
       </c>
       <c r="C7" t="n">
-        <v>828</v>
+        <v>549</v>
       </c>
       <c r="D7" t="n">
-        <v>546</v>
+        <v>564</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C8" t="n">
-        <v>324</v>
+        <v>270</v>
       </c>
       <c r="D8" t="n">
-        <v>387</v>
+        <v>384</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C9" t="n">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="D9" t="n">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="10">
@@ -6182,10 +6182,10 @@
         <v>34</v>
       </c>
       <c r="C10" t="n">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D10" t="n">
-        <v>237</v>
+        <v>242</v>
       </c>
     </row>
     <row r="11">
@@ -6196,10 +6196,10 @@
         <v>23</v>
       </c>
       <c r="C11" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D11" t="n">
-        <v>199</v>
+        <v>196</v>
       </c>
     </row>
     <row r="12">
@@ -6210,10 +6210,10 @@
         <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D12" t="n">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="13">
@@ -6227,7 +6227,7 @@
         <v>81</v>
       </c>
       <c r="D13" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="15">
@@ -6252,10 +6252,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16">
@@ -6269,7 +6269,7 @@
         <v>40</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -6280,10 +6280,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18">
@@ -6297,7 +6297,7 @@
         <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C19" t="n">
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20">
@@ -6322,10 +6322,10 @@
         <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="21">
@@ -6336,7 +6336,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D21" t="n">
         <v>7</v>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6160</v>
+        <v>6117</v>
       </c>
       <c r="C2" t="n">
-        <v>7419</v>
+        <v>5883</v>
       </c>
       <c r="D2" t="n">
-        <v>20621</v>
+        <v>21589</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4853</v>
+        <v>3986</v>
       </c>
       <c r="C3" t="n">
-        <v>7694</v>
+        <v>6211</v>
       </c>
       <c r="D3" t="n">
-        <v>12093</v>
+        <v>12102</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3331</v>
+        <v>2863</v>
       </c>
       <c r="C4" t="n">
-        <v>6053</v>
+        <v>5763</v>
       </c>
       <c r="D4" t="n">
-        <v>5342</v>
+        <v>5669</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1796</v>
+        <v>1619</v>
       </c>
       <c r="C5" t="n">
-        <v>4071</v>
+        <v>2731</v>
       </c>
       <c r="D5" t="n">
-        <v>1871</v>
+        <v>1984</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>936</v>
+        <v>812</v>
       </c>
       <c r="C6" t="n">
-        <v>2488</v>
+        <v>1718</v>
       </c>
       <c r="D6" t="n">
-        <v>915</v>
+        <v>933</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>377</v>
+        <v>335</v>
       </c>
       <c r="C7" t="n">
-        <v>1274</v>
+        <v>850</v>
       </c>
       <c r="D7" t="n">
-        <v>587</v>
+        <v>608</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>124</v>
+        <v>112</v>
       </c>
       <c r="C8" t="n">
-        <v>572</v>
+        <v>412</v>
       </c>
       <c r="D8" t="n">
-        <v>405</v>
+        <v>411</v>
       </c>
     </row>
     <row r="9">
@@ -6479,10 +6479,10 @@
         <v>53</v>
       </c>
       <c r="C9" t="n">
-        <v>265</v>
+        <v>241</v>
       </c>
       <c r="D9" t="n">
-        <v>297</v>
+        <v>294</v>
       </c>
     </row>
     <row r="10">
@@ -6493,10 +6493,10 @@
         <v>36</v>
       </c>
       <c r="C10" t="n">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="D10" t="n">
-        <v>239</v>
+        <v>246</v>
       </c>
     </row>
     <row r="11">
@@ -6507,10 +6507,10 @@
         <v>25</v>
       </c>
       <c r="C11" t="n">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="D11" t="n">
-        <v>202</v>
+        <v>199</v>
       </c>
     </row>
     <row r="12">
@@ -6521,10 +6521,10 @@
         <v>16</v>
       </c>
       <c r="C12" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D12" t="n">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C13" t="n">
         <v>89</v>
       </c>
       <c r="D13" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="14">
@@ -6549,10 +6549,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15">
@@ -6563,10 +6563,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16">
@@ -6577,10 +6577,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17">
@@ -6591,10 +6591,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18">
@@ -6605,10 +6605,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -6622,7 +6622,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="21">
@@ -6647,7 +6647,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="D21" t="n">
         <v>8</v>

--- a/output/yearly_population_iteration_49_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_49_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6921</v>
+        <v>4985</v>
       </c>
       <c r="C2" t="n">
-        <v>5584</v>
+        <v>9585</v>
       </c>
       <c r="D2" t="n">
-        <v>19900</v>
+        <v>31244</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4099</v>
+        <v>3450</v>
       </c>
       <c r="C3" t="n">
-        <v>5259</v>
+        <v>7059</v>
       </c>
       <c r="D3" t="n">
-        <v>12692</v>
+        <v>14872</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2937</v>
+        <v>2639</v>
       </c>
       <c r="C4" t="n">
-        <v>5883</v>
+        <v>7734</v>
       </c>
       <c r="D4" t="n">
-        <v>6670</v>
+        <v>8191</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1935</v>
+        <v>1649</v>
       </c>
       <c r="C5" t="n">
-        <v>4219</v>
+        <v>5320</v>
       </c>
       <c r="D5" t="n">
-        <v>2541</v>
+        <v>3249</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1093</v>
+        <v>876</v>
       </c>
       <c r="C6" t="n">
-        <v>2214</v>
+        <v>2589</v>
       </c>
       <c r="D6" t="n">
-        <v>1101</v>
+        <v>1316</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>497</v>
+        <v>404</v>
       </c>
       <c r="C7" t="n">
-        <v>1283</v>
+        <v>1205</v>
       </c>
       <c r="D7" t="n">
-        <v>649</v>
+        <v>681</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>190</v>
+        <v>150</v>
       </c>
       <c r="C8" t="n">
-        <v>618</v>
+        <v>494</v>
       </c>
       <c r="D8" t="n">
-        <v>439</v>
+        <v>435</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="C9" t="n">
-        <v>321</v>
+        <v>266</v>
       </c>
       <c r="D9" t="n">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C10" t="n">
-        <v>214</v>
+        <v>202</v>
       </c>
       <c r="D10" t="n">
-        <v>251</v>
+        <v>246</v>
       </c>
     </row>
     <row r="11">
@@ -912,7 +912,7 @@
         <v>168</v>
       </c>
       <c r="D11" t="n">
-        <v>203</v>
+        <v>206</v>
       </c>
     </row>
     <row r="12">
@@ -923,10 +923,10 @@
         <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D12" t="n">
-        <v>161</v>
+        <v>158</v>
       </c>
     </row>
     <row r="13">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -979,10 +979,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D16" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17">
@@ -996,7 +996,7 @@
         <v>38</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8994</v>
+        <v>6304</v>
       </c>
       <c r="C2" t="n">
-        <v>7729</v>
+        <v>7532</v>
       </c>
       <c r="D2" t="n">
-        <v>22603</v>
+        <v>26118</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4371</v>
+        <v>3379</v>
       </c>
       <c r="C3" t="n">
-        <v>4746</v>
+        <v>7222</v>
       </c>
       <c r="D3" t="n">
-        <v>12856</v>
+        <v>16099</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2953</v>
+        <v>2583</v>
       </c>
       <c r="C4" t="n">
-        <v>5449</v>
+        <v>7174</v>
       </c>
       <c r="D4" t="n">
-        <v>7507</v>
+        <v>8953</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2123</v>
+        <v>1828</v>
       </c>
       <c r="C5" t="n">
-        <v>4889</v>
+        <v>6344</v>
       </c>
       <c r="D5" t="n">
-        <v>3113</v>
+        <v>3956</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1331</v>
+        <v>1096</v>
       </c>
       <c r="C6" t="n">
-        <v>3134</v>
+        <v>3770</v>
       </c>
       <c r="D6" t="n">
-        <v>1321</v>
+        <v>1595</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>678</v>
+        <v>546</v>
       </c>
       <c r="C7" t="n">
-        <v>1698</v>
+        <v>1828</v>
       </c>
       <c r="D7" t="n">
-        <v>713</v>
+        <v>760</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>286</v>
+        <v>224</v>
       </c>
       <c r="C8" t="n">
-        <v>917</v>
+        <v>795</v>
       </c>
       <c r="D8" t="n">
-        <v>461</v>
+        <v>466</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>105</v>
+        <v>86</v>
       </c>
       <c r="C9" t="n">
-        <v>445</v>
+        <v>361</v>
       </c>
       <c r="D9" t="n">
-        <v>322</v>
+        <v>319</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C10" t="n">
-        <v>259</v>
+        <v>225</v>
       </c>
       <c r="D10" t="n">
-        <v>253</v>
+        <v>251</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C11" t="n">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="D11" t="n">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D12" t="n">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="13">
@@ -1248,10 +1248,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D13" t="n">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="14">
@@ -1262,10 +1262,10 @@
         <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>83</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D16" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17">
@@ -1318,7 +1318,7 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D18" t="n">
         <v>39</v>
@@ -1360,7 +1360,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D21" t="n">
         <v>10</v>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9492</v>
+        <v>6540</v>
       </c>
       <c r="C2" t="n">
-        <v>11148</v>
+        <v>6404</v>
       </c>
       <c r="D2" t="n">
-        <v>29042</v>
+        <v>24212</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5149</v>
+        <v>3701</v>
       </c>
       <c r="C3" t="n">
-        <v>5320</v>
+        <v>6515</v>
       </c>
       <c r="D3" t="n">
-        <v>13260</v>
+        <v>16325</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3012</v>
+        <v>2480</v>
       </c>
       <c r="C4" t="n">
-        <v>4966</v>
+        <v>7045</v>
       </c>
       <c r="D4" t="n">
-        <v>8028</v>
+        <v>9778</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2191</v>
+        <v>1895</v>
       </c>
       <c r="C5" t="n">
-        <v>4987</v>
+        <v>6501</v>
       </c>
       <c r="D5" t="n">
-        <v>3693</v>
+        <v>4517</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1512</v>
+        <v>1276</v>
       </c>
       <c r="C6" t="n">
-        <v>3862</v>
+        <v>4761</v>
       </c>
       <c r="D6" t="n">
-        <v>1548</v>
+        <v>1913</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>849</v>
+        <v>682</v>
       </c>
       <c r="C7" t="n">
-        <v>2285</v>
+        <v>2626</v>
       </c>
       <c r="D7" t="n">
-        <v>795</v>
+        <v>859</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>396</v>
+        <v>307</v>
       </c>
       <c r="C8" t="n">
-        <v>1238</v>
+        <v>1191</v>
       </c>
       <c r="D8" t="n">
-        <v>486</v>
+        <v>501</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>153</v>
+        <v>121</v>
       </c>
       <c r="C9" t="n">
-        <v>625</v>
+        <v>526</v>
       </c>
       <c r="D9" t="n">
-        <v>337</v>
+        <v>331</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="C10" t="n">
-        <v>329</v>
+        <v>272</v>
       </c>
       <c r="D10" t="n">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C11" t="n">
-        <v>210</v>
+        <v>194</v>
       </c>
       <c r="D11" t="n">
-        <v>210</v>
+        <v>207</v>
       </c>
     </row>
     <row r="12">
@@ -1545,10 +1545,10 @@
         <v>19</v>
       </c>
       <c r="C12" t="n">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D12" t="n">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="13">
@@ -1559,10 +1559,10 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="D13" t="n">
-        <v>130</v>
+        <v>127</v>
       </c>
     </row>
     <row r="14">
@@ -1576,7 +1576,7 @@
         <v>90</v>
       </c>
       <c r="D14" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="15">
@@ -1587,10 +1587,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D15" t="n">
-        <v>83</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -1601,10 +1601,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D16" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17">
@@ -1615,10 +1615,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -1671,7 +1671,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D21" t="n">
         <v>11</v>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8657</v>
+        <v>6028</v>
       </c>
       <c r="C2" t="n">
-        <v>7402</v>
+        <v>4354</v>
       </c>
       <c r="D2" t="n">
-        <v>23510</v>
+        <v>19996</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5900</v>
+        <v>4477</v>
       </c>
       <c r="C3" t="n">
-        <v>8577</v>
+        <v>9863</v>
       </c>
       <c r="D3" t="n">
-        <v>14841</v>
+        <v>18048</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2024</v>
+        <v>1750</v>
       </c>
       <c r="C4" t="n">
-        <v>7600</v>
+        <v>10163</v>
       </c>
       <c r="D4" t="n">
-        <v>7834</v>
+        <v>9505</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1397</v>
+        <v>1179</v>
       </c>
       <c r="C5" t="n">
-        <v>3784</v>
+        <v>4665</v>
       </c>
       <c r="D5" t="n">
-        <v>2545</v>
+        <v>3088</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>784</v>
+        <v>630</v>
       </c>
       <c r="C6" t="n">
-        <v>2239</v>
+        <v>2573</v>
       </c>
       <c r="D6" t="n">
-        <v>779</v>
+        <v>841</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>365</v>
+        <v>283</v>
       </c>
       <c r="C7" t="n">
-        <v>1213</v>
+        <v>1167</v>
       </c>
       <c r="D7" t="n">
-        <v>476</v>
+        <v>490</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>141</v>
+        <v>111</v>
       </c>
       <c r="C8" t="n">
-        <v>612</v>
+        <v>515</v>
       </c>
       <c r="D8" t="n">
-        <v>330</v>
+        <v>324</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="C9" t="n">
-        <v>322</v>
+        <v>266</v>
       </c>
       <c r="D9" t="n">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C10" t="n">
-        <v>205</v>
+        <v>190</v>
       </c>
       <c r="D10" t="n">
-        <v>205</v>
+        <v>202</v>
       </c>
     </row>
     <row r="11">
@@ -1842,10 +1842,10 @@
         <v>17</v>
       </c>
       <c r="C11" t="n">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D11" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="12">
@@ -1856,10 +1856,10 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="D12" t="n">
-        <v>127</v>
+        <v>124</v>
       </c>
     </row>
     <row r="13">
@@ -1873,7 +1873,7 @@
         <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="14">
@@ -1884,10 +1884,10 @@
         <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D14" t="n">
-        <v>81</v>
+        <v>77</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D15" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="16">
@@ -1912,10 +1912,10 @@
         <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D16" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="17">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5049</v>
+        <v>3698</v>
       </c>
       <c r="C2" t="n">
-        <v>3264</v>
+        <v>2583</v>
       </c>
       <c r="D2" t="n">
-        <v>16471</v>
+        <v>15177</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>6125</v>
+        <v>4456</v>
       </c>
       <c r="C3" t="n">
-        <v>7255</v>
+        <v>6640</v>
       </c>
       <c r="D3" t="n">
-        <v>15353</v>
+        <v>17273</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3085</v>
+        <v>2453</v>
       </c>
       <c r="C4" t="n">
-        <v>8202</v>
+        <v>10200</v>
       </c>
       <c r="D4" t="n">
-        <v>8747</v>
+        <v>10710</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1545</v>
+        <v>1309</v>
       </c>
       <c r="C5" t="n">
-        <v>5462</v>
+        <v>7061</v>
       </c>
       <c r="D5" t="n">
-        <v>3251</v>
+        <v>3854</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>951</v>
+        <v>763</v>
       </c>
       <c r="C6" t="n">
-        <v>2938</v>
+        <v>3427</v>
       </c>
       <c r="D6" t="n">
-        <v>961</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>345</v>
+        <v>266</v>
       </c>
       <c r="C7" t="n">
-        <v>1611</v>
+        <v>1655</v>
       </c>
       <c r="D7" t="n">
-        <v>517</v>
+        <v>537</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>119</v>
+        <v>96</v>
       </c>
       <c r="C8" t="n">
-        <v>802</v>
+        <v>697</v>
       </c>
       <c r="D8" t="n">
-        <v>345</v>
+        <v>339</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="C9" t="n">
-        <v>380</v>
+        <v>314</v>
       </c>
       <c r="D9" t="n">
-        <v>262</v>
+        <v>260</v>
       </c>
     </row>
     <row r="10">
@@ -2139,7 +2139,7 @@
         <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>227</v>
+        <v>215</v>
       </c>
       <c r="D10" t="n">
         <v>211</v>
@@ -2153,10 +2153,10 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="D11" t="n">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="12">
@@ -2167,10 +2167,10 @@
         <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D12" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="13">
@@ -2181,10 +2181,10 @@
         <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D13" t="n">
-        <v>101</v>
+        <v>96</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D14" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="15">
@@ -2209,10 +2209,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4876</v>
+        <v>3686</v>
       </c>
       <c r="C2" t="n">
-        <v>5235</v>
+        <v>3137</v>
       </c>
       <c r="D2" t="n">
-        <v>25772</v>
+        <v>12253</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4751</v>
+        <v>3474</v>
       </c>
       <c r="C3" t="n">
-        <v>4657</v>
+        <v>4197</v>
       </c>
       <c r="D3" t="n">
-        <v>14457</v>
+        <v>15948</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3821</v>
+        <v>2869</v>
       </c>
       <c r="C4" t="n">
-        <v>7549</v>
+        <v>8244</v>
       </c>
       <c r="D4" t="n">
-        <v>9622</v>
+        <v>11455</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1950</v>
+        <v>1589</v>
       </c>
       <c r="C5" t="n">
-        <v>6742</v>
+        <v>8390</v>
       </c>
       <c r="D5" t="n">
-        <v>4049</v>
+        <v>4789</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1108</v>
+        <v>907</v>
       </c>
       <c r="C6" t="n">
-        <v>4071</v>
+        <v>5066</v>
       </c>
       <c r="D6" t="n">
-        <v>1299</v>
+        <v>1457</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>521</v>
+        <v>407</v>
       </c>
       <c r="C7" t="n">
-        <v>2224</v>
+        <v>2434</v>
       </c>
       <c r="D7" t="n">
-        <v>576</v>
+        <v>604</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>177</v>
+        <v>137</v>
       </c>
       <c r="C8" t="n">
-        <v>1150</v>
+        <v>1088</v>
       </c>
       <c r="D8" t="n">
-        <v>368</v>
+        <v>360</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="C9" t="n">
-        <v>552</v>
+        <v>459</v>
       </c>
       <c r="D9" t="n">
-        <v>269</v>
+        <v>266</v>
       </c>
     </row>
     <row r="10">
@@ -2447,10 +2447,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C10" t="n">
-        <v>283</v>
+        <v>253</v>
       </c>
       <c r="D10" t="n">
         <v>216</v>
@@ -2464,10 +2464,10 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>194</v>
+        <v>185</v>
       </c>
       <c r="D11" t="n">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="12">
@@ -2478,10 +2478,10 @@
         <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D12" t="n">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D13" t="n">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D14" t="n">
-        <v>66</v>
+        <v>63</v>
       </c>
     </row>
     <row r="15">
@@ -2520,7 +2520,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D15" t="n">
         <v>48</v>
@@ -2562,7 +2562,7 @@
         <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D18" t="n">
         <v>13</v>
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2888</v>
+        <v>2192</v>
       </c>
       <c r="C2" t="n">
-        <v>2371</v>
+        <v>1491</v>
       </c>
       <c r="D2" t="n">
-        <v>17767</v>
+        <v>8551</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4610</v>
+        <v>3400</v>
       </c>
       <c r="C3" t="n">
-        <v>4703</v>
+        <v>3713</v>
       </c>
       <c r="D3" t="n">
-        <v>15377</v>
+        <v>15206</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4205</v>
+        <v>3152</v>
       </c>
       <c r="C4" t="n">
-        <v>7189</v>
+        <v>7543</v>
       </c>
       <c r="D4" t="n">
-        <v>10255</v>
+        <v>12090</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2022</v>
+        <v>1643</v>
       </c>
       <c r="C5" t="n">
-        <v>7845</v>
+        <v>9560</v>
       </c>
       <c r="D5" t="n">
-        <v>4383</v>
+        <v>5038</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>942</v>
+        <v>744</v>
       </c>
       <c r="C6" t="n">
-        <v>4958</v>
+        <v>5963</v>
       </c>
       <c r="D6" t="n">
-        <v>1281</v>
+        <v>1418</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>163</v>
+        <v>126</v>
       </c>
       <c r="C7" t="n">
-        <v>2258</v>
+        <v>2357</v>
       </c>
       <c r="D7" t="n">
-        <v>584</v>
+        <v>599</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="C8" t="n">
-        <v>912</v>
+        <v>780</v>
       </c>
       <c r="D8" t="n">
-        <v>387</v>
+        <v>380</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>277</v>
+        <v>247</v>
       </c>
       <c r="D9" t="n">
-        <v>293</v>
+        <v>289</v>
       </c>
     </row>
     <row r="10">
@@ -2761,10 +2761,10 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>190</v>
+        <v>181</v>
       </c>
       <c r="D10" t="n">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="11">
@@ -2775,10 +2775,10 @@
         <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D11" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D12" t="n">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="13">
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D13" t="n">
-        <v>64</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14">
@@ -2817,7 +2817,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D14" t="n">
         <v>47</v>
@@ -2859,7 +2859,7 @@
         <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D17" t="n">
         <v>12</v>
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3920</v>
+        <v>2587</v>
       </c>
       <c r="C2" t="n">
-        <v>3090</v>
+        <v>6648</v>
       </c>
       <c r="D2" t="n">
-        <v>13201</v>
+        <v>16242</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3327</v>
+        <v>2486</v>
       </c>
       <c r="C3" t="n">
-        <v>3179</v>
+        <v>2414</v>
       </c>
       <c r="D3" t="n">
-        <v>14668</v>
+        <v>13425</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3828</v>
+        <v>2848</v>
       </c>
       <c r="C4" t="n">
-        <v>5891</v>
+        <v>5584</v>
       </c>
       <c r="D4" t="n">
-        <v>10779</v>
+        <v>12201</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2577</v>
+        <v>1999</v>
       </c>
       <c r="C5" t="n">
-        <v>7454</v>
+        <v>8542</v>
       </c>
       <c r="D5" t="n">
-        <v>5151</v>
+        <v>5900</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1243</v>
+        <v>987</v>
       </c>
       <c r="C6" t="n">
-        <v>6207</v>
+        <v>7485</v>
       </c>
       <c r="D6" t="n">
-        <v>1723</v>
+        <v>1886</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>361</v>
+        <v>277</v>
       </c>
       <c r="C7" t="n">
-        <v>3412</v>
+        <v>3851</v>
       </c>
       <c r="D7" t="n">
-        <v>666</v>
+        <v>703</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>77</v>
+        <v>62</v>
       </c>
       <c r="C8" t="n">
-        <v>1430</v>
+        <v>1366</v>
       </c>
       <c r="D8" t="n">
-        <v>410</v>
+        <v>403</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C9" t="n">
-        <v>496</v>
+        <v>426</v>
       </c>
       <c r="D9" t="n">
-        <v>302</v>
+        <v>296</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>222</v>
+        <v>206</v>
       </c>
       <c r="D10" t="n">
-        <v>177</v>
+        <v>173</v>
       </c>
     </row>
     <row r="11">
@@ -3086,10 +3086,10 @@
         <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="D11" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D12" t="n">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D13" t="n">
-        <v>64</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14">
@@ -3128,7 +3128,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D14" t="n">
         <v>47</v>
@@ -3170,7 +3170,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D17" t="n">
         <v>10</v>
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D18" t="n">
         <v>2</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3059</v>
+        <v>1970</v>
       </c>
       <c r="C2" t="n">
-        <v>2467</v>
+        <v>3427</v>
       </c>
       <c r="D2" t="n">
-        <v>9375</v>
+        <v>11763</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3084</v>
+        <v>2207</v>
       </c>
       <c r="C3" t="n">
-        <v>2876</v>
+        <v>3737</v>
       </c>
       <c r="D3" t="n">
-        <v>13694</v>
+        <v>13032</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3357</v>
+        <v>2528</v>
       </c>
       <c r="C4" t="n">
-        <v>4762</v>
+        <v>4296</v>
       </c>
       <c r="D4" t="n">
-        <v>11077</v>
+        <v>12111</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2830</v>
+        <v>2140</v>
       </c>
       <c r="C5" t="n">
-        <v>7000</v>
+        <v>7613</v>
       </c>
       <c r="D5" t="n">
-        <v>5741</v>
+        <v>6559</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1493</v>
+        <v>1172</v>
       </c>
       <c r="C6" t="n">
-        <v>6862</v>
+        <v>8125</v>
       </c>
       <c r="D6" t="n">
-        <v>2032</v>
+        <v>2265</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>340</v>
+        <v>250</v>
       </c>
       <c r="C7" t="n">
-        <v>4356</v>
+        <v>5003</v>
       </c>
       <c r="D7" t="n">
-        <v>748</v>
+        <v>786</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="C8" t="n">
-        <v>1905</v>
+        <v>1896</v>
       </c>
       <c r="D8" t="n">
-        <v>433</v>
+        <v>416</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C9" t="n">
-        <v>596</v>
+        <v>507</v>
       </c>
       <c r="D9" t="n">
-        <v>300</v>
+        <v>294</v>
       </c>
     </row>
     <row r="10">
@@ -3383,10 +3383,10 @@
         <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>230</v>
+        <v>215</v>
       </c>
       <c r="D10" t="n">
-        <v>180</v>
+        <v>177</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="D11" t="n">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D12" t="n">
-        <v>95</v>
+        <v>92</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D13" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="14">
@@ -3467,7 +3467,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D16" t="n">
         <v>9</v>
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
         <v>1</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5492</v>
+        <v>2751</v>
       </c>
       <c r="C2" t="n">
-        <v>10190</v>
+        <v>5610</v>
       </c>
       <c r="D2" t="n">
-        <v>12431</v>
+        <v>10759</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2585</v>
+        <v>1786</v>
       </c>
       <c r="C3" t="n">
-        <v>2426</v>
+        <v>3242</v>
       </c>
       <c r="D3" t="n">
-        <v>12374</v>
+        <v>12045</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2831</v>
+        <v>2098</v>
       </c>
       <c r="C4" t="n">
-        <v>3802</v>
+        <v>3970</v>
       </c>
       <c r="D4" t="n">
-        <v>11010</v>
+        <v>11875</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2779</v>
+        <v>2096</v>
       </c>
       <c r="C5" t="n">
-        <v>5976</v>
+        <v>6117</v>
       </c>
       <c r="D5" t="n">
-        <v>6334</v>
+        <v>7105</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1816</v>
+        <v>1392</v>
       </c>
       <c r="C6" t="n">
-        <v>6857</v>
+        <v>7860</v>
       </c>
       <c r="D6" t="n">
-        <v>2504</v>
+        <v>2771</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>632</v>
+        <v>476</v>
       </c>
       <c r="C7" t="n">
-        <v>5312</v>
+        <v>6163</v>
       </c>
       <c r="D7" t="n">
-        <v>903</v>
+        <v>944</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>126</v>
+        <v>94</v>
       </c>
       <c r="C8" t="n">
-        <v>2811</v>
+        <v>3009</v>
       </c>
       <c r="D8" t="n">
-        <v>465</v>
+        <v>459</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="C9" t="n">
-        <v>1031</v>
+        <v>960</v>
       </c>
       <c r="D9" t="n">
-        <v>311</v>
+        <v>302</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C10" t="n">
-        <v>349</v>
+        <v>302</v>
       </c>
       <c r="D10" t="n">
-        <v>191</v>
+        <v>185</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="D11" t="n">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="D12" t="n">
-        <v>97</v>
+        <v>93</v>
       </c>
     </row>
     <row r="13">
@@ -3736,7 +3736,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D13" t="n">
         <v>65</v>
@@ -3778,7 +3778,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D16" t="n">
         <v>8</v>
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5682</v>
+        <v>3955</v>
       </c>
       <c r="C2" t="n">
-        <v>4811</v>
+        <v>2341</v>
       </c>
       <c r="D2" t="n">
-        <v>6231</v>
+        <v>13599</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3885</v>
+        <v>1968</v>
       </c>
       <c r="C2" t="n">
-        <v>5706</v>
+        <v>3186</v>
       </c>
       <c r="D2" t="n">
-        <v>9149</v>
+        <v>7918</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3622</v>
+        <v>2425</v>
       </c>
       <c r="C3" t="n">
-        <v>4495</v>
+        <v>4071</v>
       </c>
       <c r="D3" t="n">
-        <v>13414</v>
+        <v>13049</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3984</v>
+        <v>3004</v>
       </c>
       <c r="C4" t="n">
-        <v>5707</v>
+        <v>6032</v>
       </c>
       <c r="D4" t="n">
-        <v>11289</v>
+        <v>12307</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1780</v>
+        <v>1344</v>
       </c>
       <c r="C5" t="n">
-        <v>9267</v>
+        <v>10155</v>
       </c>
       <c r="D5" t="n">
-        <v>5848</v>
+        <v>6473</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>583</v>
+        <v>439</v>
       </c>
       <c r="C6" t="n">
-        <v>6616</v>
+        <v>7580</v>
       </c>
       <c r="D6" t="n">
-        <v>1996</v>
+        <v>2162</v>
       </c>
     </row>
     <row r="7">
@@ -4271,10 +4271,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>116</v>
+        <v>86</v>
       </c>
       <c r="C7" t="n">
-        <v>2754</v>
+        <v>2948</v>
       </c>
       <c r="D7" t="n">
         <v>570</v>
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C8" t="n">
-        <v>1010</v>
+        <v>940</v>
       </c>
       <c r="D8" t="n">
-        <v>304</v>
+        <v>295</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>342</v>
+        <v>295</v>
       </c>
       <c r="D9" t="n">
-        <v>187</v>
+        <v>181</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="D10" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="D11" t="n">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="12">
@@ -4344,7 +4344,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D12" t="n">
         <v>63</v>
@@ -4386,7 +4386,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D15" t="n">
         <v>7</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6269</v>
+        <v>5367</v>
       </c>
       <c r="C2" t="n">
-        <v>3299</v>
+        <v>4264</v>
       </c>
       <c r="D2" t="n">
-        <v>15458</v>
+        <v>23697</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2414</v>
+        <v>1682</v>
       </c>
       <c r="C3" t="n">
-        <v>2463</v>
+        <v>1179</v>
       </c>
       <c r="D3" t="n">
-        <v>1735</v>
+        <v>2923</v>
       </c>
     </row>
     <row r="4">
@@ -4655,7 +4655,7 @@
         <v>26</v>
       </c>
       <c r="C12" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D12" t="n">
         <v>199</v>
@@ -4669,7 +4669,7 @@
         <v>19</v>
       </c>
       <c r="C13" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D13" t="n">
         <v>170</v>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4628</v>
+        <v>4144</v>
       </c>
       <c r="C2" t="n">
-        <v>3301</v>
+        <v>4280</v>
       </c>
       <c r="D2" t="n">
-        <v>13245</v>
+        <v>20161</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3565</v>
+        <v>2891</v>
       </c>
       <c r="C3" t="n">
-        <v>2534</v>
+        <v>2545</v>
       </c>
       <c r="D3" t="n">
-        <v>3912</v>
+        <v>6197</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1082</v>
+        <v>764</v>
       </c>
       <c r="C4" t="n">
-        <v>1509</v>
+        <v>745</v>
       </c>
       <c r="D4" t="n">
-        <v>1530</v>
+        <v>1770</v>
       </c>
     </row>
     <row r="5">
@@ -4879,7 +4879,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C6" t="n">
         <v>411</v>
@@ -4893,7 +4893,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C7" t="n">
         <v>409</v>
@@ -4966,7 +4966,7 @@
         <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D12" t="n">
         <v>206</v>
@@ -4994,7 +4994,7 @@
         <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D14" t="n">
         <v>148</v>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6001</v>
+        <v>5061</v>
       </c>
       <c r="C2" t="n">
-        <v>7350</v>
+        <v>8355</v>
       </c>
       <c r="D2" t="n">
-        <v>26381</v>
+        <v>32634</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3369</v>
+        <v>2913</v>
       </c>
       <c r="C3" t="n">
-        <v>2557</v>
+        <v>3021</v>
       </c>
       <c r="D3" t="n">
-        <v>5123</v>
+        <v>7985</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1998</v>
+        <v>1545</v>
       </c>
       <c r="C4" t="n">
-        <v>2068</v>
+        <v>1741</v>
       </c>
       <c r="D4" t="n">
-        <v>1926</v>
+        <v>2549</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>503</v>
+        <v>374</v>
       </c>
       <c r="C5" t="n">
-        <v>933</v>
+        <v>507</v>
       </c>
       <c r="D5" t="n">
-        <v>1215</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="6">
@@ -5218,7 +5218,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C8" t="n">
         <v>355</v>
@@ -5238,7 +5238,7 @@
         <v>268</v>
       </c>
       <c r="D9" t="n">
-        <v>368</v>
+        <v>372</v>
       </c>
     </row>
     <row r="10">
@@ -5252,7 +5252,7 @@
         <v>210</v>
       </c>
       <c r="D10" t="n">
-        <v>350</v>
+        <v>346</v>
       </c>
     </row>
     <row r="11">
@@ -5277,7 +5277,7 @@
         <v>30</v>
       </c>
       <c r="C12" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D12" t="n">
         <v>211</v>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6247</v>
+        <v>4799</v>
       </c>
       <c r="C2" t="n">
-        <v>4111</v>
+        <v>7856</v>
       </c>
       <c r="D2" t="n">
-        <v>27572</v>
+        <v>26798</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3777</v>
+        <v>3218</v>
       </c>
       <c r="C3" t="n">
-        <v>4407</v>
+        <v>5056</v>
       </c>
       <c r="D3" t="n">
-        <v>7993</v>
+        <v>11169</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2268</v>
+        <v>1877</v>
       </c>
       <c r="C4" t="n">
-        <v>2292</v>
+        <v>2405</v>
       </c>
       <c r="D4" t="n">
-        <v>2432</v>
+        <v>3438</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1043</v>
+        <v>799</v>
       </c>
       <c r="C5" t="n">
-        <v>1512</v>
+        <v>1148</v>
       </c>
       <c r="D5" t="n">
-        <v>1307</v>
+        <v>1458</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>281</v>
+        <v>229</v>
       </c>
       <c r="C6" t="n">
-        <v>617</v>
+        <v>400</v>
       </c>
       <c r="D6" t="n">
-        <v>941</v>
+        <v>958</v>
       </c>
     </row>
     <row r="7">
@@ -5521,7 +5521,7 @@
         <v>354</v>
       </c>
       <c r="D7" t="n">
-        <v>668</v>
+        <v>659</v>
       </c>
     </row>
     <row r="8">
@@ -5549,7 +5549,7 @@
         <v>306</v>
       </c>
       <c r="D9" t="n">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C10" t="n">
         <v>236</v>
       </c>
       <c r="D10" t="n">
-        <v>349</v>
+        <v>346</v>
       </c>
     </row>
     <row r="11">
@@ -5588,7 +5588,7 @@
         <v>33</v>
       </c>
       <c r="C12" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D12" t="n">
         <v>218</v>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6500</v>
+        <v>6538</v>
       </c>
       <c r="C2" t="n">
-        <v>12561</v>
+        <v>15077</v>
       </c>
       <c r="D2" t="n">
-        <v>25422</v>
+        <v>27935</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3637</v>
+        <v>2914</v>
       </c>
       <c r="C3" t="n">
-        <v>3481</v>
+        <v>5333</v>
       </c>
       <c r="D3" t="n">
-        <v>9789</v>
+        <v>12003</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1875</v>
+        <v>1580</v>
       </c>
       <c r="C4" t="n">
-        <v>2853</v>
+        <v>3192</v>
       </c>
       <c r="D4" t="n">
-        <v>2923</v>
+        <v>4112</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>877</v>
+        <v>705</v>
       </c>
       <c r="C5" t="n">
-        <v>1395</v>
+        <v>1318</v>
       </c>
       <c r="D5" t="n">
-        <v>1193</v>
+        <v>1439</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>315</v>
+        <v>245</v>
       </c>
       <c r="C6" t="n">
-        <v>726</v>
+        <v>528</v>
       </c>
       <c r="D6" t="n">
-        <v>756</v>
+        <v>786</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="C7" t="n">
-        <v>308</v>
+        <v>239</v>
       </c>
       <c r="D7" t="n">
-        <v>524</v>
+        <v>521</v>
       </c>
     </row>
     <row r="8">
@@ -5846,7 +5846,7 @@
         <v>224</v>
       </c>
       <c r="D8" t="n">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="9">
@@ -5860,7 +5860,7 @@
         <v>199</v>
       </c>
       <c r="D9" t="n">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="10">
@@ -5874,7 +5874,7 @@
         <v>150</v>
       </c>
       <c r="D10" t="n">
-        <v>239</v>
+        <v>237</v>
       </c>
     </row>
     <row r="11">
@@ -5899,7 +5899,7 @@
         <v>14</v>
       </c>
       <c r="C12" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D12" t="n">
         <v>149</v>
@@ -5913,7 +5913,7 @@
         <v>9</v>
       </c>
       <c r="C13" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D13" t="n">
         <v>116</v>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5352</v>
+        <v>4771</v>
       </c>
       <c r="C2" t="n">
-        <v>6820</v>
+        <v>9879</v>
       </c>
       <c r="D2" t="n">
-        <v>18751</v>
+        <v>24842</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4233</v>
+        <v>3991</v>
       </c>
       <c r="C3" t="n">
-        <v>7701</v>
+        <v>9562</v>
       </c>
       <c r="D3" t="n">
-        <v>11804</v>
+        <v>13904</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2440</v>
+        <v>1962</v>
       </c>
       <c r="C4" t="n">
-        <v>3185</v>
+        <v>4441</v>
       </c>
       <c r="D4" t="n">
-        <v>4284</v>
+        <v>5653</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1227</v>
+        <v>1025</v>
       </c>
       <c r="C5" t="n">
-        <v>2247</v>
+        <v>2405</v>
       </c>
       <c r="D5" t="n">
-        <v>1494</v>
+        <v>1934</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>561</v>
+        <v>441</v>
       </c>
       <c r="C6" t="n">
-        <v>1108</v>
+        <v>976</v>
       </c>
       <c r="D6" t="n">
-        <v>833</v>
+        <v>892</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>188</v>
+        <v>152</v>
       </c>
       <c r="C7" t="n">
-        <v>549</v>
+        <v>400</v>
       </c>
       <c r="D7" t="n">
-        <v>564</v>
+        <v>567</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="C8" t="n">
-        <v>270</v>
+        <v>232</v>
       </c>
       <c r="D8" t="n">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C9" t="n">
         <v>212</v>
       </c>
       <c r="D9" t="n">
-        <v>284</v>
+        <v>282</v>
       </c>
     </row>
     <row r="10">
@@ -6185,7 +6185,7 @@
         <v>175</v>
       </c>
       <c r="D10" t="n">
-        <v>242</v>
+        <v>240</v>
       </c>
     </row>
     <row r="11">
@@ -6199,7 +6199,7 @@
         <v>132</v>
       </c>
       <c r="D11" t="n">
-        <v>196</v>
+        <v>198</v>
       </c>
     </row>
     <row r="12">
@@ -6210,10 +6210,10 @@
         <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="D12" t="n">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="13">
@@ -6224,7 +6224,7 @@
         <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D13" t="n">
         <v>119</v>
@@ -6238,10 +6238,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D14" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15">
@@ -6255,7 +6255,7 @@
         <v>50</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -6283,7 +6283,7 @@
         <v>36</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -6297,7 +6297,7 @@
         <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -6325,7 +6325,7 @@
         <v>29</v>
       </c>
       <c r="D20" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21">
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6117</v>
+        <v>4865</v>
       </c>
       <c r="C2" t="n">
-        <v>5883</v>
+        <v>7785</v>
       </c>
       <c r="D2" t="n">
-        <v>21589</v>
+        <v>22889</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3986</v>
+        <v>3608</v>
       </c>
       <c r="C3" t="n">
-        <v>6211</v>
+        <v>8413</v>
       </c>
       <c r="D3" t="n">
-        <v>12102</v>
+        <v>14652</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2863</v>
+        <v>2569</v>
       </c>
       <c r="C4" t="n">
-        <v>5763</v>
+        <v>7298</v>
       </c>
       <c r="D4" t="n">
-        <v>5669</v>
+        <v>7011</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1619</v>
+        <v>1304</v>
       </c>
       <c r="C5" t="n">
-        <v>2731</v>
+        <v>3488</v>
       </c>
       <c r="D5" t="n">
-        <v>1984</v>
+        <v>2589</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>812</v>
+        <v>669</v>
       </c>
       <c r="C6" t="n">
-        <v>1718</v>
+        <v>1732</v>
       </c>
       <c r="D6" t="n">
-        <v>933</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>335</v>
+        <v>262</v>
       </c>
       <c r="C7" t="n">
-        <v>850</v>
+        <v>700</v>
       </c>
       <c r="D7" t="n">
-        <v>608</v>
+        <v>612</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>112</v>
+        <v>96</v>
       </c>
       <c r="C8" t="n">
-        <v>412</v>
+        <v>319</v>
       </c>
       <c r="D8" t="n">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C9" t="n">
-        <v>241</v>
+        <v>221</v>
       </c>
       <c r="D9" t="n">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="10">
@@ -6493,10 +6493,10 @@
         <v>36</v>
       </c>
       <c r="C10" t="n">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D10" t="n">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="11">
@@ -6507,10 +6507,10 @@
         <v>25</v>
       </c>
       <c r="C11" t="n">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D11" t="n">
-        <v>199</v>
+        <v>202</v>
       </c>
     </row>
     <row r="12">
@@ -6524,7 +6524,7 @@
         <v>115</v>
       </c>
       <c r="D12" t="n">
-        <v>159</v>
+        <v>155</v>
       </c>
     </row>
     <row r="13">
@@ -6532,10 +6532,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D13" t="n">
         <v>122</v>
@@ -6552,7 +6552,7 @@
         <v>71</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="15">
@@ -6563,10 +6563,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D15" t="n">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -6594,7 +6594,7 @@
         <v>37</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -6636,7 +6636,7 @@
         <v>29</v>
       </c>
       <c r="D20" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21">

--- a/output/yearly_population_iteration_49_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_49_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4985</v>
+        <v>1063</v>
       </c>
       <c r="C2" t="n">
-        <v>9585</v>
+        <v>2278</v>
       </c>
       <c r="D2" t="n">
-        <v>31244</v>
+        <v>13699</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3450</v>
+        <v>1736</v>
       </c>
       <c r="C3" t="n">
-        <v>7059</v>
+        <v>6315</v>
       </c>
       <c r="D3" t="n">
-        <v>14872</v>
+        <v>15088</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2639</v>
+        <v>1299</v>
       </c>
       <c r="C4" t="n">
-        <v>7734</v>
+        <v>8218</v>
       </c>
       <c r="D4" t="n">
-        <v>8191</v>
+        <v>6707</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1649</v>
+        <v>694</v>
       </c>
       <c r="C5" t="n">
-        <v>5320</v>
+        <v>4039</v>
       </c>
       <c r="D5" t="n">
-        <v>3249</v>
+        <v>2114</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>876</v>
+        <v>277</v>
       </c>
       <c r="C6" t="n">
-        <v>2589</v>
+        <v>1090</v>
       </c>
       <c r="D6" t="n">
-        <v>1316</v>
+        <v>776</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>404</v>
+        <v>101</v>
       </c>
       <c r="C7" t="n">
-        <v>1205</v>
+        <v>456</v>
       </c>
       <c r="D7" t="n">
-        <v>681</v>
+        <v>492</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>150</v>
+        <v>74</v>
       </c>
       <c r="C8" t="n">
-        <v>494</v>
+        <v>330</v>
       </c>
       <c r="D8" t="n">
-        <v>435</v>
+        <v>373</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="C9" t="n">
-        <v>266</v>
+        <v>290</v>
       </c>
       <c r="D9" t="n">
-        <v>308</v>
+        <v>319</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="C10" t="n">
-        <v>202</v>
+        <v>215</v>
       </c>
       <c r="D10" t="n">
-        <v>246</v>
+        <v>269</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="C11" t="n">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="D11" t="n">
-        <v>206</v>
+        <v>211</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>129</v>
+        <v>111</v>
       </c>
       <c r="D12" t="n">
-        <v>158</v>
+        <v>174</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>99</v>
+        <v>78</v>
       </c>
       <c r="D13" t="n">
-        <v>125</v>
+        <v>139</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>89</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>53</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>37</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>22</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>142</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6304</v>
+        <v>1919</v>
       </c>
       <c r="C2" t="n">
-        <v>7532</v>
+        <v>4197</v>
       </c>
       <c r="D2" t="n">
-        <v>26118</v>
+        <v>14614</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3379</v>
+        <v>1192</v>
       </c>
       <c r="C3" t="n">
-        <v>7222</v>
+        <v>3621</v>
       </c>
       <c r="D3" t="n">
-        <v>16099</v>
+        <v>13779</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2583</v>
+        <v>1314</v>
       </c>
       <c r="C4" t="n">
-        <v>7174</v>
+        <v>6987</v>
       </c>
       <c r="D4" t="n">
-        <v>8953</v>
+        <v>8112</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1828</v>
+        <v>865</v>
       </c>
       <c r="C5" t="n">
-        <v>6344</v>
+        <v>6240</v>
       </c>
       <c r="D5" t="n">
-        <v>3956</v>
+        <v>2907</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1096</v>
+        <v>424</v>
       </c>
       <c r="C6" t="n">
-        <v>3770</v>
+        <v>2589</v>
       </c>
       <c r="D6" t="n">
-        <v>1595</v>
+        <v>983</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>546</v>
+        <v>157</v>
       </c>
       <c r="C7" t="n">
-        <v>1828</v>
+        <v>770</v>
       </c>
       <c r="D7" t="n">
-        <v>760</v>
+        <v>531</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>224</v>
+        <v>79</v>
       </c>
       <c r="C8" t="n">
-        <v>795</v>
+        <v>394</v>
       </c>
       <c r="D8" t="n">
-        <v>466</v>
+        <v>386</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>86</v>
+        <v>57</v>
       </c>
       <c r="C9" t="n">
-        <v>361</v>
+        <v>309</v>
       </c>
       <c r="D9" t="n">
-        <v>319</v>
+        <v>326</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="C10" t="n">
-        <v>225</v>
+        <v>248</v>
       </c>
       <c r="D10" t="n">
-        <v>251</v>
+        <v>274</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="C11" t="n">
-        <v>181</v>
+        <v>194</v>
       </c>
       <c r="D11" t="n">
-        <v>206</v>
+        <v>216</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>142</v>
+        <v>133</v>
       </c>
       <c r="D12" t="n">
-        <v>162</v>
+        <v>176</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>109</v>
+        <v>89</v>
       </c>
       <c r="D13" t="n">
-        <v>126</v>
+        <v>142</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C14" t="n">
-        <v>84</v>
+        <v>71</v>
       </c>
       <c r="D14" t="n">
-        <v>101</v>
+        <v>93</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>52</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>35</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>95</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>18</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>79</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>106</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6540</v>
+        <v>1004</v>
       </c>
       <c r="C2" t="n">
-        <v>6404</v>
+        <v>1696</v>
       </c>
       <c r="D2" t="n">
-        <v>24212</v>
+        <v>9867</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3701</v>
+        <v>1349</v>
       </c>
       <c r="C3" t="n">
-        <v>6515</v>
+        <v>3694</v>
       </c>
       <c r="D3" t="n">
-        <v>16325</v>
+        <v>13511</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2480</v>
+        <v>1434</v>
       </c>
       <c r="C4" t="n">
-        <v>7045</v>
+        <v>6222</v>
       </c>
       <c r="D4" t="n">
-        <v>9778</v>
+        <v>8907</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1895</v>
+        <v>883</v>
       </c>
       <c r="C5" t="n">
-        <v>6501</v>
+        <v>7156</v>
       </c>
       <c r="D5" t="n">
-        <v>4517</v>
+        <v>3344</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1276</v>
+        <v>339</v>
       </c>
       <c r="C6" t="n">
-        <v>4761</v>
+        <v>3512</v>
       </c>
       <c r="D6" t="n">
-        <v>1913</v>
+        <v>996</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>682</v>
+        <v>74</v>
       </c>
       <c r="C7" t="n">
-        <v>2626</v>
+        <v>801</v>
       </c>
       <c r="D7" t="n">
-        <v>859</v>
+        <v>559</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>307</v>
+        <v>52</v>
       </c>
       <c r="C8" t="n">
-        <v>1191</v>
+        <v>445</v>
       </c>
       <c r="D8" t="n">
-        <v>501</v>
+        <v>436</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>121</v>
+        <v>28</v>
       </c>
       <c r="C9" t="n">
-        <v>526</v>
+        <v>243</v>
       </c>
       <c r="D9" t="n">
-        <v>331</v>
+        <v>370</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>52</v>
+        <v>14</v>
       </c>
       <c r="C10" t="n">
-        <v>272</v>
+        <v>190</v>
       </c>
       <c r="D10" t="n">
-        <v>257</v>
+        <v>211</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>194</v>
+        <v>130</v>
       </c>
       <c r="D11" t="n">
-        <v>207</v>
+        <v>172</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="C12" t="n">
-        <v>155</v>
+        <v>87</v>
       </c>
       <c r="D12" t="n">
-        <v>165</v>
+        <v>139</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>118</v>
+        <v>69</v>
       </c>
       <c r="D13" t="n">
-        <v>127</v>
+        <v>91</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>90</v>
+        <v>62</v>
       </c>
       <c r="D14" t="n">
-        <v>102</v>
+        <v>70</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C16" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>34</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="C17" t="n">
-        <v>42</v>
+        <v>93</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>17</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>35</v>
+        <v>77</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>112</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6028</v>
+        <v>620</v>
       </c>
       <c r="C2" t="n">
-        <v>4354</v>
+        <v>4439</v>
       </c>
       <c r="D2" t="n">
-        <v>19996</v>
+        <v>15628</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4477</v>
+        <v>1009</v>
       </c>
       <c r="C3" t="n">
-        <v>9863</v>
+        <v>2333</v>
       </c>
       <c r="D3" t="n">
-        <v>18048</v>
+        <v>12005</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1750</v>
+        <v>1238</v>
       </c>
       <c r="C4" t="n">
-        <v>10163</v>
+        <v>4793</v>
       </c>
       <c r="D4" t="n">
-        <v>9505</v>
+        <v>9475</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1179</v>
+        <v>1014</v>
       </c>
       <c r="C5" t="n">
-        <v>4665</v>
+        <v>6600</v>
       </c>
       <c r="D5" t="n">
-        <v>3088</v>
+        <v>4235</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>630</v>
+        <v>514</v>
       </c>
       <c r="C6" t="n">
-        <v>2573</v>
+        <v>5293</v>
       </c>
       <c r="D6" t="n">
-        <v>841</v>
+        <v>1343</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>283</v>
+        <v>150</v>
       </c>
       <c r="C7" t="n">
-        <v>1167</v>
+        <v>2038</v>
       </c>
       <c r="D7" t="n">
-        <v>490</v>
+        <v>623</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>111</v>
+        <v>56</v>
       </c>
       <c r="C8" t="n">
-        <v>515</v>
+        <v>600</v>
       </c>
       <c r="D8" t="n">
-        <v>324</v>
+        <v>451</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="C9" t="n">
-        <v>266</v>
+        <v>325</v>
       </c>
       <c r="D9" t="n">
-        <v>251</v>
+        <v>376</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="C10" t="n">
-        <v>190</v>
+        <v>214</v>
       </c>
       <c r="D10" t="n">
-        <v>202</v>
+        <v>227</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D11" t="n">
-        <v>161</v>
+        <v>177</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>115</v>
+        <v>101</v>
       </c>
       <c r="D12" t="n">
-        <v>124</v>
+        <v>145</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="D13" t="n">
-        <v>99</v>
+        <v>91</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C14" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>77</v>
+        <v>70</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>51</v>
+        <v>67</v>
       </c>
       <c r="D15" t="n">
-        <v>64</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="C16" t="n">
-        <v>41</v>
+        <v>90</v>
       </c>
       <c r="D16" t="n">
-        <v>49</v>
+        <v>30</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>34</v>
+        <v>103</v>
       </c>
       <c r="D17" t="n">
-        <v>38</v>
+        <v>11</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="D18" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>112</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3698</v>
+        <v>469</v>
       </c>
       <c r="C2" t="n">
-        <v>2583</v>
+        <v>3047</v>
       </c>
       <c r="D2" t="n">
-        <v>15177</v>
+        <v>11370</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4456</v>
+        <v>753</v>
       </c>
       <c r="C3" t="n">
-        <v>6640</v>
+        <v>2966</v>
       </c>
       <c r="D3" t="n">
-        <v>17273</v>
+        <v>11806</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2453</v>
+        <v>1068</v>
       </c>
       <c r="C4" t="n">
-        <v>10200</v>
+        <v>3650</v>
       </c>
       <c r="D4" t="n">
-        <v>10710</v>
+        <v>9666</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1309</v>
+        <v>1063</v>
       </c>
       <c r="C5" t="n">
-        <v>7061</v>
+        <v>5935</v>
       </c>
       <c r="D5" t="n">
-        <v>3854</v>
+        <v>4891</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>763</v>
+        <v>619</v>
       </c>
       <c r="C6" t="n">
-        <v>3427</v>
+        <v>6050</v>
       </c>
       <c r="D6" t="n">
-        <v>1071</v>
+        <v>1658</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>266</v>
+        <v>174</v>
       </c>
       <c r="C7" t="n">
-        <v>1655</v>
+        <v>3165</v>
       </c>
       <c r="D7" t="n">
-        <v>537</v>
+        <v>701</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>96</v>
+        <v>53</v>
       </c>
       <c r="C8" t="n">
-        <v>697</v>
+        <v>968</v>
       </c>
       <c r="D8" t="n">
-        <v>339</v>
+        <v>485</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="C9" t="n">
-        <v>314</v>
+        <v>412</v>
       </c>
       <c r="D9" t="n">
-        <v>260</v>
+        <v>374</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C10" t="n">
-        <v>215</v>
+        <v>233</v>
       </c>
       <c r="D10" t="n">
-        <v>211</v>
+        <v>235</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>168</v>
+        <v>157</v>
       </c>
       <c r="D11" t="n">
-        <v>166</v>
+        <v>185</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>97</v>
+        <v>110</v>
       </c>
       <c r="D12" t="n">
-        <v>131</v>
+        <v>137</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D13" t="n">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="D14" t="n">
-        <v>62</v>
+        <v>55</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>40</v>
+        <v>88</v>
       </c>
       <c r="D15" t="n">
-        <v>48</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>33</v>
+        <v>100</v>
       </c>
       <c r="D16" t="n">
-        <v>37</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="D17" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3686</v>
+        <v>1516</v>
       </c>
       <c r="C2" t="n">
-        <v>3137</v>
+        <v>6006</v>
       </c>
       <c r="D2" t="n">
-        <v>12253</v>
+        <v>14605</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3474</v>
+        <v>533</v>
       </c>
       <c r="C3" t="n">
-        <v>4197</v>
+        <v>2634</v>
       </c>
       <c r="D3" t="n">
-        <v>15948</v>
+        <v>11044</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2869</v>
+        <v>824</v>
       </c>
       <c r="C4" t="n">
-        <v>8244</v>
+        <v>3267</v>
       </c>
       <c r="D4" t="n">
-        <v>11455</v>
+        <v>9628</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1589</v>
+        <v>973</v>
       </c>
       <c r="C5" t="n">
-        <v>8390</v>
+        <v>4736</v>
       </c>
       <c r="D5" t="n">
-        <v>4789</v>
+        <v>5521</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>907</v>
+        <v>740</v>
       </c>
       <c r="C6" t="n">
-        <v>5066</v>
+        <v>5998</v>
       </c>
       <c r="D6" t="n">
-        <v>1457</v>
+        <v>2132</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>407</v>
+        <v>307</v>
       </c>
       <c r="C7" t="n">
-        <v>2434</v>
+        <v>4407</v>
       </c>
       <c r="D7" t="n">
-        <v>604</v>
+        <v>834</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>137</v>
+        <v>84</v>
       </c>
       <c r="C8" t="n">
-        <v>1088</v>
+        <v>1881</v>
       </c>
       <c r="D8" t="n">
-        <v>360</v>
+        <v>514</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="C9" t="n">
-        <v>459</v>
+        <v>628</v>
       </c>
       <c r="D9" t="n">
-        <v>266</v>
+        <v>383</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C10" t="n">
-        <v>253</v>
+        <v>300</v>
       </c>
       <c r="D10" t="n">
-        <v>216</v>
+        <v>247</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C11" t="n">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D11" t="n">
-        <v>169</v>
+        <v>189</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="D12" t="n">
-        <v>133</v>
+        <v>140</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="D13" t="n">
-        <v>99</v>
+        <v>96</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="D14" t="n">
-        <v>63</v>
+        <v>57</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C15" t="n">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="D15" t="n">
-        <v>48</v>
+        <v>28</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>36</v>
+        <v>104</v>
       </c>
       <c r="D16" t="n">
-        <v>36</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2192</v>
+        <v>1006</v>
       </c>
       <c r="C2" t="n">
-        <v>1491</v>
+        <v>3076</v>
       </c>
       <c r="D2" t="n">
-        <v>8551</v>
+        <v>10515</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3400</v>
+        <v>884</v>
       </c>
       <c r="C3" t="n">
-        <v>3713</v>
+        <v>3803</v>
       </c>
       <c r="D3" t="n">
-        <v>15206</v>
+        <v>12126</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3152</v>
+        <v>1304</v>
       </c>
       <c r="C4" t="n">
-        <v>7543</v>
+        <v>4773</v>
       </c>
       <c r="D4" t="n">
-        <v>12090</v>
+        <v>10052</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1643</v>
+        <v>755</v>
       </c>
       <c r="C5" t="n">
-        <v>9560</v>
+        <v>7714</v>
       </c>
       <c r="D5" t="n">
-        <v>5038</v>
+        <v>5137</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>744</v>
+        <v>283</v>
       </c>
       <c r="C6" t="n">
-        <v>5963</v>
+        <v>5847</v>
       </c>
       <c r="D6" t="n">
-        <v>1418</v>
+        <v>1781</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>126</v>
+        <v>77</v>
       </c>
       <c r="C7" t="n">
-        <v>2357</v>
+        <v>1843</v>
       </c>
       <c r="D7" t="n">
-        <v>599</v>
+        <v>626</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="C8" t="n">
-        <v>780</v>
+        <v>615</v>
       </c>
       <c r="D8" t="n">
-        <v>380</v>
+        <v>375</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="C9" t="n">
-        <v>247</v>
+        <v>294</v>
       </c>
       <c r="D9" t="n">
-        <v>289</v>
+        <v>242</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="D10" t="n">
-        <v>165</v>
+        <v>185</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="D11" t="n">
-        <v>130</v>
+        <v>137</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="D12" t="n">
-        <v>97</v>
+        <v>94</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>43</v>
+        <v>86</v>
       </c>
       <c r="D14" t="n">
-        <v>47</v>
+        <v>27</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>35</v>
+        <v>101</v>
       </c>
       <c r="D15" t="n">
-        <v>35</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2587</v>
+        <v>512</v>
       </c>
       <c r="C2" t="n">
-        <v>6648</v>
+        <v>1537</v>
       </c>
       <c r="D2" t="n">
-        <v>16242</v>
+        <v>7213</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2486</v>
+        <v>785</v>
       </c>
       <c r="C3" t="n">
-        <v>2414</v>
+        <v>3024</v>
       </c>
       <c r="D3" t="n">
-        <v>13425</v>
+        <v>11024</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2848</v>
+        <v>916</v>
       </c>
       <c r="C4" t="n">
-        <v>5584</v>
+        <v>4052</v>
       </c>
       <c r="D4" t="n">
-        <v>12201</v>
+        <v>9689</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1999</v>
+        <v>710</v>
       </c>
       <c r="C5" t="n">
-        <v>8542</v>
+        <v>5542</v>
       </c>
       <c r="D5" t="n">
-        <v>5900</v>
+        <v>5215</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>987</v>
+        <v>279</v>
       </c>
       <c r="C6" t="n">
-        <v>7485</v>
+        <v>5545</v>
       </c>
       <c r="D6" t="n">
-        <v>1886</v>
+        <v>1923</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>277</v>
+        <v>68</v>
       </c>
       <c r="C7" t="n">
-        <v>3851</v>
+        <v>2573</v>
       </c>
       <c r="D7" t="n">
-        <v>703</v>
+        <v>624</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>62</v>
+        <v>15</v>
       </c>
       <c r="C8" t="n">
-        <v>1366</v>
+        <v>721</v>
       </c>
       <c r="D8" t="n">
-        <v>403</v>
+        <v>326</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="C9" t="n">
-        <v>426</v>
+        <v>264</v>
       </c>
       <c r="D9" t="n">
-        <v>296</v>
+        <v>194</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>206</v>
+        <v>133</v>
       </c>
       <c r="D10" t="n">
-        <v>173</v>
+        <v>141</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>134</v>
+        <v>78</v>
       </c>
       <c r="D11" t="n">
-        <v>136</v>
+        <v>100</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>82</v>
+        <v>55</v>
       </c>
       <c r="D12" t="n">
-        <v>98</v>
+        <v>63</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>32</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="D14" t="n">
-        <v>47</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1970</v>
+        <v>519</v>
       </c>
       <c r="C2" t="n">
-        <v>3427</v>
+        <v>5585</v>
       </c>
       <c r="D2" t="n">
-        <v>11763</v>
+        <v>11447</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2207</v>
+        <v>545</v>
       </c>
       <c r="C3" t="n">
-        <v>3737</v>
+        <v>1898</v>
       </c>
       <c r="D3" t="n">
-        <v>13032</v>
+        <v>9620</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2528</v>
+        <v>749</v>
       </c>
       <c r="C4" t="n">
-        <v>4296</v>
+        <v>3414</v>
       </c>
       <c r="D4" t="n">
-        <v>12111</v>
+        <v>9650</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2140</v>
+        <v>732</v>
       </c>
       <c r="C5" t="n">
-        <v>7613</v>
+        <v>4611</v>
       </c>
       <c r="D5" t="n">
-        <v>6559</v>
+        <v>5872</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1172</v>
+        <v>436</v>
       </c>
       <c r="C6" t="n">
-        <v>8125</v>
+        <v>5534</v>
       </c>
       <c r="D6" t="n">
-        <v>2265</v>
+        <v>2465</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>250</v>
+        <v>142</v>
       </c>
       <c r="C7" t="n">
-        <v>5003</v>
+        <v>4111</v>
       </c>
       <c r="D7" t="n">
-        <v>786</v>
+        <v>834</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="C8" t="n">
-        <v>1896</v>
+        <v>1617</v>
       </c>
       <c r="D8" t="n">
-        <v>416</v>
+        <v>369</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C9" t="n">
-        <v>507</v>
+        <v>472</v>
       </c>
       <c r="D9" t="n">
-        <v>294</v>
+        <v>211</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C10" t="n">
-        <v>215</v>
+        <v>189</v>
       </c>
       <c r="D10" t="n">
-        <v>177</v>
+        <v>148</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>133</v>
+        <v>101</v>
       </c>
       <c r="D11" t="n">
-        <v>136</v>
+        <v>103</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>79</v>
+        <v>64</v>
       </c>
       <c r="D12" t="n">
-        <v>92</v>
+        <v>66</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="D13" t="n">
-        <v>63</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="D14" t="n">
-        <v>37</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>56</v>
+        <v>11</v>
       </c>
       <c r="D15" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3484,7 +3484,7 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2751</v>
+        <v>477</v>
       </c>
       <c r="C2" t="n">
-        <v>5610</v>
+        <v>4938</v>
       </c>
       <c r="D2" t="n">
-        <v>10759</v>
+        <v>22428</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1786</v>
+        <v>441</v>
       </c>
       <c r="C3" t="n">
-        <v>3242</v>
+        <v>3277</v>
       </c>
       <c r="D3" t="n">
-        <v>12045</v>
+        <v>9220</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2098</v>
+        <v>570</v>
       </c>
       <c r="C4" t="n">
-        <v>3970</v>
+        <v>2542</v>
       </c>
       <c r="D4" t="n">
-        <v>11875</v>
+        <v>9351</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2096</v>
+        <v>673</v>
       </c>
       <c r="C5" t="n">
-        <v>6117</v>
+        <v>3906</v>
       </c>
       <c r="D5" t="n">
-        <v>7105</v>
+        <v>6346</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1392</v>
+        <v>525</v>
       </c>
       <c r="C6" t="n">
-        <v>7860</v>
+        <v>5023</v>
       </c>
       <c r="D6" t="n">
-        <v>2771</v>
+        <v>2963</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>476</v>
+        <v>242</v>
       </c>
       <c r="C7" t="n">
-        <v>6163</v>
+        <v>4792</v>
       </c>
       <c r="D7" t="n">
-        <v>944</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>94</v>
+        <v>68</v>
       </c>
       <c r="C8" t="n">
-        <v>3009</v>
+        <v>2765</v>
       </c>
       <c r="D8" t="n">
-        <v>459</v>
+        <v>438</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="C9" t="n">
-        <v>960</v>
+        <v>976</v>
       </c>
       <c r="D9" t="n">
-        <v>302</v>
+        <v>232</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="D10" t="n">
-        <v>185</v>
+        <v>153</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>155</v>
+        <v>136</v>
       </c>
       <c r="D11" t="n">
-        <v>139</v>
+        <v>108</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>93</v>
+        <v>78</v>
       </c>
       <c r="D12" t="n">
-        <v>93</v>
+        <v>70</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="D13" t="n">
-        <v>65</v>
+        <v>37</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="D14" t="n">
-        <v>38</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>58</v>
+        <v>25</v>
       </c>
       <c r="D15" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>69</v>
+        <v>3</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3955</v>
+        <v>2980</v>
       </c>
       <c r="C2" t="n">
-        <v>2341</v>
+        <v>3670</v>
       </c>
       <c r="D2" t="n">
-        <v>13599</v>
+        <v>10114</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>843</v>
+        <v>855</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>175</v>
+        <v>205</v>
       </c>
       <c r="C4" t="n">
-        <v>313</v>
+        <v>344</v>
       </c>
       <c r="D4" t="n">
-        <v>1805</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>249</v>
+        <v>314</v>
       </c>
       <c r="C5" t="n">
-        <v>515</v>
+        <v>586</v>
       </c>
       <c r="D5" t="n">
-        <v>1038</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>182</v>
+        <v>255</v>
       </c>
       <c r="C6" t="n">
-        <v>395</v>
+        <v>488</v>
       </c>
       <c r="D6" t="n">
-        <v>777</v>
+        <v>898</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>129</v>
+        <v>202</v>
       </c>
       <c r="C7" t="n">
-        <v>293</v>
+        <v>388</v>
       </c>
       <c r="D7" t="n">
-        <v>496</v>
+        <v>596</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>99</v>
+        <v>171</v>
       </c>
       <c r="C8" t="n">
-        <v>222</v>
+        <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>420</v>
+        <v>531</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>75</v>
+        <v>136</v>
       </c>
       <c r="C9" t="n">
-        <v>187</v>
+        <v>277</v>
       </c>
       <c r="D9" t="n">
-        <v>349</v>
+        <v>445</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>53</v>
+        <v>105</v>
       </c>
       <c r="C10" t="n">
-        <v>173</v>
+        <v>265</v>
       </c>
       <c r="D10" t="n">
-        <v>362</v>
+        <v>485</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>34</v>
+        <v>71</v>
       </c>
       <c r="C11" t="n">
-        <v>137</v>
+        <v>215</v>
       </c>
       <c r="D11" t="n">
-        <v>245</v>
+        <v>327</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="C12" t="n">
-        <v>104</v>
+        <v>169</v>
       </c>
       <c r="D12" t="n">
-        <v>196</v>
+        <v>274</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="C13" t="n">
-        <v>84</v>
+        <v>142</v>
       </c>
       <c r="D13" t="n">
-        <v>168</v>
+        <v>234</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C14" t="n">
-        <v>75</v>
+        <v>128</v>
       </c>
       <c r="D14" t="n">
-        <v>145</v>
+        <v>207</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C15" t="n">
-        <v>72</v>
+        <v>127</v>
       </c>
       <c r="D15" t="n">
-        <v>117</v>
+        <v>171</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>124</v>
       </c>
       <c r="D16" t="n">
-        <v>97</v>
+        <v>140</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="C17" t="n">
-        <v>66</v>
+        <v>119</v>
       </c>
       <c r="D17" t="n">
-        <v>76</v>
+        <v>114</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C18" t="n">
-        <v>63</v>
+        <v>116</v>
       </c>
       <c r="D18" t="n">
-        <v>57</v>
+        <v>85</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C19" t="n">
-        <v>60</v>
+        <v>111</v>
       </c>
       <c r="D19" t="n">
-        <v>38</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>109</v>
       </c>
       <c r="D20" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="21">
@@ -4156,10 +4156,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C21" t="n">
-        <v>72</v>
+        <v>131</v>
       </c>
       <c r="D21" t="n">
         <v>1</v>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1968</v>
+        <v>596</v>
       </c>
       <c r="C2" t="n">
-        <v>3186</v>
+        <v>10251</v>
       </c>
       <c r="D2" t="n">
-        <v>7918</v>
+        <v>24714</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2425</v>
+        <v>378</v>
       </c>
       <c r="C3" t="n">
-        <v>4071</v>
+        <v>3548</v>
       </c>
       <c r="D3" t="n">
-        <v>13049</v>
+        <v>10396</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3004</v>
+        <v>449</v>
       </c>
       <c r="C4" t="n">
-        <v>6032</v>
+        <v>2841</v>
       </c>
       <c r="D4" t="n">
-        <v>12307</v>
+        <v>9045</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1344</v>
+        <v>573</v>
       </c>
       <c r="C5" t="n">
-        <v>10155</v>
+        <v>3158</v>
       </c>
       <c r="D5" t="n">
-        <v>6473</v>
+        <v>6553</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>439</v>
+        <v>548</v>
       </c>
       <c r="C6" t="n">
-        <v>7580</v>
+        <v>4469</v>
       </c>
       <c r="D6" t="n">
-        <v>2162</v>
+        <v>3442</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>86</v>
+        <v>322</v>
       </c>
       <c r="C7" t="n">
-        <v>2948</v>
+        <v>4891</v>
       </c>
       <c r="D7" t="n">
-        <v>570</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>20</v>
+        <v>121</v>
       </c>
       <c r="C8" t="n">
-        <v>940</v>
+        <v>3590</v>
       </c>
       <c r="D8" t="n">
-        <v>295</v>
+        <v>530</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="C9" t="n">
-        <v>295</v>
+        <v>1711</v>
       </c>
       <c r="D9" t="n">
-        <v>181</v>
+        <v>257</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C10" t="n">
-        <v>151</v>
+        <v>569</v>
       </c>
       <c r="D10" t="n">
-        <v>136</v>
+        <v>160</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>91</v>
+        <v>198</v>
       </c>
       <c r="D11" t="n">
-        <v>91</v>
+        <v>112</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>50</v>
+        <v>98</v>
       </c>
       <c r="D12" t="n">
-        <v>63</v>
+        <v>73</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>38</v>
+        <v>64</v>
       </c>
       <c r="D13" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
         <v>56</v>
       </c>
       <c r="D14" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>67</v>
+        <v>34</v>
       </c>
       <c r="D15" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5367</v>
+        <v>6004</v>
       </c>
       <c r="C2" t="n">
-        <v>4264</v>
+        <v>4668</v>
       </c>
       <c r="D2" t="n">
-        <v>23697</v>
+        <v>25138</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1682</v>
+        <v>987</v>
       </c>
       <c r="C3" t="n">
-        <v>1179</v>
+        <v>1449</v>
       </c>
       <c r="D3" t="n">
-        <v>2923</v>
+        <v>1998</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="C4" t="n">
-        <v>114</v>
+        <v>134</v>
       </c>
       <c r="D4" t="n">
-        <v>1538</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>191</v>
+        <v>148</v>
       </c>
       <c r="C5" t="n">
-        <v>384</v>
+        <v>334</v>
       </c>
       <c r="D5" t="n">
-        <v>1161</v>
+        <v>986</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>202</v>
+        <v>143</v>
       </c>
       <c r="C6" t="n">
-        <v>459</v>
+        <v>360</v>
       </c>
       <c r="D6" t="n">
-        <v>808</v>
+        <v>712</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>102</v>
       </c>
       <c r="C7" t="n">
-        <v>350</v>
+        <v>277</v>
       </c>
       <c r="D7" t="n">
-        <v>546</v>
+        <v>466</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="C8" t="n">
-        <v>260</v>
+        <v>206</v>
       </c>
       <c r="D8" t="n">
-        <v>429</v>
+        <v>384</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="C9" t="n">
-        <v>205</v>
+        <v>169</v>
       </c>
       <c r="D9" t="n">
-        <v>354</v>
+        <v>313</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="C10" t="n">
-        <v>180</v>
+        <v>151</v>
       </c>
       <c r="D10" t="n">
-        <v>356</v>
+        <v>324</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="C11" t="n">
-        <v>154</v>
+        <v>129</v>
       </c>
       <c r="D11" t="n">
-        <v>261</v>
+        <v>231</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C12" t="n">
-        <v>119</v>
+        <v>100</v>
       </c>
       <c r="D12" t="n">
-        <v>199</v>
+        <v>182</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="D13" t="n">
-        <v>170</v>
+        <v>154</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>133</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>118</v>
+        <v>111</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>89</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="D18" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>10</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C21" t="n">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4144</v>
+        <v>2707</v>
       </c>
       <c r="C2" t="n">
-        <v>4280</v>
+        <v>7584</v>
       </c>
       <c r="D2" t="n">
-        <v>20161</v>
+        <v>25247</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2891</v>
+        <v>2980</v>
       </c>
       <c r="C3" t="n">
-        <v>2545</v>
+        <v>2914</v>
       </c>
       <c r="D3" t="n">
-        <v>6197</v>
+        <v>5920</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>764</v>
+        <v>483</v>
       </c>
       <c r="C4" t="n">
-        <v>745</v>
+        <v>951</v>
       </c>
       <c r="D4" t="n">
-        <v>1770</v>
+        <v>1518</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>125</v>
+        <v>98</v>
       </c>
       <c r="C5" t="n">
-        <v>220</v>
+        <v>206</v>
       </c>
       <c r="D5" t="n">
-        <v>1186</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>185</v>
+        <v>137</v>
       </c>
       <c r="C6" t="n">
-        <v>411</v>
+        <v>340</v>
       </c>
       <c r="D6" t="n">
-        <v>864</v>
+        <v>756</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>159</v>
+        <v>114</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>324</v>
       </c>
       <c r="D7" t="n">
-        <v>589</v>
+        <v>509</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>115</v>
+        <v>83</v>
       </c>
       <c r="C8" t="n">
-        <v>307</v>
+        <v>245</v>
       </c>
       <c r="D8" t="n">
-        <v>441</v>
+        <v>395</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="C9" t="n">
-        <v>230</v>
+        <v>190</v>
       </c>
       <c r="D9" t="n">
-        <v>363</v>
+        <v>319</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="C10" t="n">
-        <v>192</v>
+        <v>160</v>
       </c>
       <c r="D10" t="n">
-        <v>352</v>
+        <v>318</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>139</v>
       </c>
       <c r="D11" t="n">
-        <v>270</v>
+        <v>244</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C12" t="n">
-        <v>135</v>
+        <v>113</v>
       </c>
       <c r="D12" t="n">
-        <v>206</v>
+        <v>186</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>170</v>
+        <v>156</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>134</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C15" t="n">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>90</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>9</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C21" t="n">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="D21" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5061</v>
+        <v>1995</v>
       </c>
       <c r="C2" t="n">
-        <v>8355</v>
+        <v>7248</v>
       </c>
       <c r="D2" t="n">
-        <v>32634</v>
+        <v>22703</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2913</v>
+        <v>2344</v>
       </c>
       <c r="C3" t="n">
-        <v>3021</v>
+        <v>4857</v>
       </c>
       <c r="D3" t="n">
-        <v>7985</v>
+        <v>8731</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1545</v>
+        <v>1521</v>
       </c>
       <c r="C4" t="n">
-        <v>1741</v>
+        <v>2118</v>
       </c>
       <c r="D4" t="n">
-        <v>2549</v>
+        <v>2344</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>374</v>
+        <v>256</v>
       </c>
       <c r="C5" t="n">
-        <v>507</v>
+        <v>637</v>
       </c>
       <c r="D5" t="n">
-        <v>1262</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>147</v>
+        <v>111</v>
       </c>
       <c r="C6" t="n">
-        <v>303</v>
+        <v>259</v>
       </c>
       <c r="D6" t="n">
-        <v>910</v>
+        <v>799</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>160</v>
+        <v>117</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>332</v>
       </c>
       <c r="D7" t="n">
-        <v>625</v>
+        <v>549</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>124</v>
+        <v>90</v>
       </c>
       <c r="C8" t="n">
-        <v>355</v>
+        <v>287</v>
       </c>
       <c r="D8" t="n">
-        <v>462</v>
+        <v>407</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>91</v>
+        <v>68</v>
       </c>
       <c r="C9" t="n">
-        <v>268</v>
+        <v>218</v>
       </c>
       <c r="D9" t="n">
-        <v>372</v>
+        <v>329</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="C10" t="n">
-        <v>210</v>
+        <v>174</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>314</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="C11" t="n">
-        <v>177</v>
+        <v>149</v>
       </c>
       <c r="D11" t="n">
-        <v>280</v>
+        <v>250</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="C12" t="n">
-        <v>147</v>
+        <v>124</v>
       </c>
       <c r="D12" t="n">
-        <v>211</v>
+        <v>193</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C13" t="n">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>173</v>
+        <v>158</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="D14" t="n">
-        <v>149</v>
+        <v>134</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C15" t="n">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="D15" t="n">
-        <v>121</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C21" t="n">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4799</v>
+        <v>2187</v>
       </c>
       <c r="C2" t="n">
-        <v>7856</v>
+        <v>8846</v>
       </c>
       <c r="D2" t="n">
-        <v>26798</v>
+        <v>22561</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3218</v>
+        <v>1796</v>
       </c>
       <c r="C3" t="n">
-        <v>5056</v>
+        <v>5344</v>
       </c>
       <c r="D3" t="n">
-        <v>11169</v>
+        <v>10337</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1877</v>
+        <v>1672</v>
       </c>
       <c r="C4" t="n">
-        <v>2405</v>
+        <v>3651</v>
       </c>
       <c r="D4" t="n">
-        <v>3438</v>
+        <v>3476</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>799</v>
+        <v>747</v>
       </c>
       <c r="C5" t="n">
-        <v>1148</v>
+        <v>1448</v>
       </c>
       <c r="D5" t="n">
-        <v>1458</v>
+        <v>1307</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>229</v>
+        <v>167</v>
       </c>
       <c r="C6" t="n">
-        <v>400</v>
+        <v>459</v>
       </c>
       <c r="D6" t="n">
-        <v>958</v>
+        <v>843</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>107</v>
       </c>
       <c r="C7" t="n">
-        <v>354</v>
+        <v>293</v>
       </c>
       <c r="D7" t="n">
-        <v>659</v>
+        <v>582</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>129</v>
+        <v>94</v>
       </c>
       <c r="C8" t="n">
-        <v>381</v>
+        <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>484</v>
+        <v>427</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>97</v>
+        <v>72</v>
       </c>
       <c r="C9" t="n">
-        <v>306</v>
+        <v>252</v>
       </c>
       <c r="D9" t="n">
-        <v>378</v>
+        <v>338</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>70</v>
+        <v>53</v>
       </c>
       <c r="C10" t="n">
-        <v>236</v>
+        <v>195</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>310</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="C11" t="n">
-        <v>191</v>
+        <v>160</v>
       </c>
       <c r="D11" t="n">
-        <v>284</v>
+        <v>257</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C12" t="n">
-        <v>158</v>
+        <v>134</v>
       </c>
       <c r="D12" t="n">
-        <v>218</v>
+        <v>199</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C13" t="n">
-        <v>128</v>
+        <v>108</v>
       </c>
       <c r="D13" t="n">
-        <v>176</v>
+        <v>159</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="D14" t="n">
-        <v>149</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C15" t="n">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="D15" t="n">
-        <v>123</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C16" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C17" t="n">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C18" t="n">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>61</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C21" t="n">
-        <v>137</v>
+        <v>120</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6538</v>
+        <v>1537</v>
       </c>
       <c r="C2" t="n">
-        <v>15077</v>
+        <v>8498</v>
       </c>
       <c r="D2" t="n">
-        <v>27935</v>
+        <v>31188</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2914</v>
+        <v>1635</v>
       </c>
       <c r="C3" t="n">
-        <v>5333</v>
+        <v>6239</v>
       </c>
       <c r="D3" t="n">
-        <v>12003</v>
+        <v>11467</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1580</v>
+        <v>1503</v>
       </c>
       <c r="C4" t="n">
-        <v>3192</v>
+        <v>4501</v>
       </c>
       <c r="D4" t="n">
-        <v>4112</v>
+        <v>4588</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>705</v>
+        <v>1041</v>
       </c>
       <c r="C5" t="n">
-        <v>1318</v>
+        <v>2567</v>
       </c>
       <c r="D5" t="n">
-        <v>1439</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>245</v>
+        <v>391</v>
       </c>
       <c r="C6" t="n">
-        <v>528</v>
+        <v>966</v>
       </c>
       <c r="D6" t="n">
-        <v>786</v>
+        <v>903</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>84</v>
+        <v>124</v>
       </c>
       <c r="C7" t="n">
-        <v>239</v>
+        <v>377</v>
       </c>
       <c r="D7" t="n">
-        <v>521</v>
+        <v>622</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>58</v>
+        <v>92</v>
       </c>
       <c r="C8" t="n">
-        <v>224</v>
+        <v>300</v>
       </c>
       <c r="D8" t="n">
-        <v>360</v>
+        <v>448</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>44</v>
+        <v>75</v>
       </c>
       <c r="C9" t="n">
-        <v>199</v>
+        <v>277</v>
       </c>
       <c r="D9" t="n">
-        <v>273</v>
+        <v>345</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="C10" t="n">
-        <v>150</v>
+        <v>220</v>
       </c>
       <c r="D10" t="n">
-        <v>237</v>
+        <v>311</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="C11" t="n">
-        <v>116</v>
+        <v>175</v>
       </c>
       <c r="D11" t="n">
-        <v>193</v>
+        <v>262</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>93</v>
+        <v>143</v>
       </c>
       <c r="D12" t="n">
-        <v>149</v>
+        <v>202</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="C13" t="n">
-        <v>73</v>
+        <v>118</v>
       </c>
       <c r="D13" t="n">
-        <v>116</v>
+        <v>162</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>58</v>
+        <v>94</v>
       </c>
       <c r="D14" t="n">
-        <v>97</v>
+        <v>136</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>45</v>
+        <v>77</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C16" t="n">
-        <v>38</v>
+        <v>67</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>76</v>
+        <v>133</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4771</v>
+        <v>2031</v>
       </c>
       <c r="C2" t="n">
-        <v>9879</v>
+        <v>7809</v>
       </c>
       <c r="D2" t="n">
-        <v>24842</v>
+        <v>26210</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3991</v>
+        <v>1319</v>
       </c>
       <c r="C3" t="n">
-        <v>9562</v>
+        <v>6426</v>
       </c>
       <c r="D3" t="n">
-        <v>13904</v>
+        <v>13517</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1962</v>
+        <v>1356</v>
       </c>
       <c r="C4" t="n">
-        <v>4441</v>
+        <v>5308</v>
       </c>
       <c r="D4" t="n">
-        <v>5653</v>
+        <v>5593</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1025</v>
+        <v>1108</v>
       </c>
       <c r="C5" t="n">
-        <v>2405</v>
+        <v>3479</v>
       </c>
       <c r="D5" t="n">
-        <v>1934</v>
+        <v>2117</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>441</v>
+        <v>620</v>
       </c>
       <c r="C6" t="n">
-        <v>976</v>
+        <v>1714</v>
       </c>
       <c r="D6" t="n">
-        <v>892</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>152</v>
+        <v>214</v>
       </c>
       <c r="C7" t="n">
-        <v>400</v>
+        <v>659</v>
       </c>
       <c r="D7" t="n">
-        <v>567</v>
+        <v>662</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>65</v>
+        <v>98</v>
       </c>
       <c r="C8" t="n">
-        <v>232</v>
+        <v>335</v>
       </c>
       <c r="D8" t="n">
-        <v>386</v>
+        <v>470</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>46</v>
+        <v>75</v>
       </c>
       <c r="C9" t="n">
-        <v>212</v>
+        <v>287</v>
       </c>
       <c r="D9" t="n">
-        <v>282</v>
+        <v>353</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>34</v>
+        <v>59</v>
       </c>
       <c r="C10" t="n">
-        <v>175</v>
+        <v>241</v>
       </c>
       <c r="D10" t="n">
-        <v>240</v>
+        <v>312</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="C11" t="n">
-        <v>132</v>
+        <v>193</v>
       </c>
       <c r="D11" t="n">
-        <v>198</v>
+        <v>266</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="C12" t="n">
-        <v>104</v>
+        <v>155</v>
       </c>
       <c r="D12" t="n">
-        <v>152</v>
+        <v>205</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C13" t="n">
-        <v>82</v>
+        <v>127</v>
       </c>
       <c r="D13" t="n">
-        <v>119</v>
+        <v>165</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>64</v>
+        <v>101</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>136</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>50</v>
+        <v>82</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>115</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C16" t="n">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>93</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>63</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="C21" t="n">
-        <v>85</v>
+        <v>145</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4865</v>
+        <v>1827</v>
       </c>
       <c r="C2" t="n">
-        <v>7785</v>
+        <v>4747</v>
       </c>
       <c r="D2" t="n">
-        <v>22889</v>
+        <v>20468</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3608</v>
+        <v>2076</v>
       </c>
       <c r="C3" t="n">
-        <v>8413</v>
+        <v>9400</v>
       </c>
       <c r="D3" t="n">
-        <v>14652</v>
+        <v>15032</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2569</v>
+        <v>1023</v>
       </c>
       <c r="C4" t="n">
-        <v>7298</v>
+        <v>6702</v>
       </c>
       <c r="D4" t="n">
-        <v>7011</v>
+        <v>5214</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1304</v>
+        <v>572</v>
       </c>
       <c r="C5" t="n">
-        <v>3488</v>
+        <v>1679</v>
       </c>
       <c r="D5" t="n">
-        <v>2589</v>
+        <v>1614</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>669</v>
+        <v>197</v>
       </c>
       <c r="C6" t="n">
-        <v>1732</v>
+        <v>645</v>
       </c>
       <c r="D6" t="n">
-        <v>1069</v>
+        <v>648</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>262</v>
+        <v>90</v>
       </c>
       <c r="C7" t="n">
-        <v>700</v>
+        <v>328</v>
       </c>
       <c r="D7" t="n">
-        <v>612</v>
+        <v>460</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>96</v>
+        <v>69</v>
       </c>
       <c r="C8" t="n">
-        <v>319</v>
+        <v>281</v>
       </c>
       <c r="D8" t="n">
-        <v>413</v>
+        <v>345</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C9" t="n">
-        <v>221</v>
+        <v>236</v>
       </c>
       <c r="D9" t="n">
-        <v>293</v>
+        <v>305</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C10" t="n">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="D10" t="n">
-        <v>244</v>
+        <v>260</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C11" t="n">
         <v>151</v>
       </c>
       <c r="D11" t="n">
-        <v>202</v>
+        <v>200</v>
       </c>
     </row>
     <row r="12">
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="D12" t="n">
-        <v>155</v>
+        <v>161</v>
       </c>
     </row>
     <row r="13">
@@ -6535,10 +6535,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>122</v>
+        <v>133</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C14" t="n">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>112</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C15" t="n">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>91</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C16" t="n">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>74</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
     </row>
     <row r="18">
@@ -6602,13 +6602,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>145</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>93</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
